--- a/research/traditional_assets/database/data/malaysia/malaysia_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_retail_grocery_and_food.xlsx
@@ -1157,13 +1157,13 @@
         <v>496.1</v>
       </c>
       <c r="L2">
-        <v>678.716513620968</v>
+        <v>678.716513620967</v>
       </c>
       <c r="M2">
         <v>721.8</v>
       </c>
       <c r="N2">
-        <v>784.232513620968</v>
+        <v>784.232513620967</v>
       </c>
       <c r="O2">
         <v>314.8</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07791311886813103</v>
+        <v>0.07776032738284749</v>
       </c>
       <c r="C2">
-        <v>806.0529332731264</v>
+        <v>801.371442079309</v>
       </c>
       <c r="D2">
-        <v>716.9529332731264</v>
+        <v>720.380442079309</v>
       </c>
       <c r="E2">
-        <v>-314.8</v>
+        <v>-306.691</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.109000000000002</v>
       </c>
       <c r="G2">
         <v>89.09999999999999</v>
@@ -1457,28 +1457,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4078827</v>
       </c>
       <c r="N2">
-        <v>49.73333333333333</v>
+        <v>49.32545063333333</v>
       </c>
       <c r="O2">
-        <v>11.936</v>
+        <v>11.838108152</v>
       </c>
       <c r="P2">
-        <v>37.79733333333333</v>
+        <v>37.48734248133333</v>
       </c>
       <c r="Q2">
-        <v>59.39733333333334</v>
+        <v>59.08734248133332</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07791311886813103</v>
+        <v>0.07815964382105808</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5456300833866089</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.930479849558</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07776032738284749</v>
+        <v>0.07760753589756399</v>
       </c>
       <c r="C3">
-        <v>801.371442079309</v>
+        <v>796.722879821766</v>
       </c>
       <c r="D3">
-        <v>720.380442079309</v>
+        <v>723.840879821766</v>
       </c>
       <c r="E3">
-        <v>-306.691</v>
+        <v>-298.582</v>
       </c>
       <c r="F3">
-        <v>8.109000000000002</v>
+        <v>16.218</v>
       </c>
       <c r="G3">
         <v>89.09999999999999</v>
@@ -1539,28 +1539,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M3">
-        <v>0.4078827</v>
+        <v>0.8157654000000001</v>
       </c>
       <c r="N3">
-        <v>49.32545063333333</v>
+        <v>48.91756793333333</v>
       </c>
       <c r="O3">
-        <v>11.838108152</v>
+        <v>11.740216304</v>
       </c>
       <c r="P3">
-        <v>37.48734248133333</v>
+        <v>37.17735162933333</v>
       </c>
       <c r="Q3">
-        <v>59.08734248133332</v>
+        <v>58.77735162933332</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07815964382105808</v>
+        <v>0.07841119989547346</v>
       </c>
       <c r="T3">
-        <v>0.5456300833866089</v>
+        <v>0.5498716801921444</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.930479849558</v>
+        <v>60.96523992477902</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07760753589756399</v>
+        <v>0.07745474441228049</v>
       </c>
       <c r="C4">
-        <v>796.722879821766</v>
+        <v>792.1077233258055</v>
       </c>
       <c r="D4">
-        <v>723.840879821766</v>
+        <v>727.3347233258055</v>
       </c>
       <c r="E4">
-        <v>-298.582</v>
+        <v>-290.473</v>
       </c>
       <c r="F4">
-        <v>16.218</v>
+        <v>24.327</v>
       </c>
       <c r="G4">
         <v>89.09999999999999</v>
@@ -1621,28 +1621,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M4">
-        <v>0.8157654000000001</v>
+        <v>1.2236481</v>
       </c>
       <c r="N4">
-        <v>48.91756793333333</v>
+        <v>48.50968523333334</v>
       </c>
       <c r="O4">
-        <v>11.740216304</v>
+        <v>11.642324456</v>
       </c>
       <c r="P4">
-        <v>37.17735162933333</v>
+        <v>36.86736077733333</v>
       </c>
       <c r="Q4">
-        <v>58.77735162933332</v>
+        <v>58.46736077733333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07841119989547346</v>
+        <v>0.07866794269307267</v>
       </c>
       <c r="T4">
-        <v>0.5498716801921444</v>
+        <v>0.5542007326019179</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.96523992477902</v>
+        <v>40.64349328318602</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07745474441228049</v>
+        <v>0.07730195292699696</v>
       </c>
       <c r="C5">
-        <v>792.1077233258055</v>
+        <v>787.5264586675722</v>
       </c>
       <c r="D5">
-        <v>727.3347233258055</v>
+        <v>730.8624586675722</v>
       </c>
       <c r="E5">
-        <v>-290.473</v>
+        <v>-282.364</v>
       </c>
       <c r="F5">
-        <v>24.327</v>
+        <v>32.43600000000001</v>
       </c>
       <c r="G5">
         <v>89.09999999999999</v>
@@ -1703,28 +1703,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M5">
-        <v>1.2236481</v>
+        <v>1.6315308</v>
       </c>
       <c r="N5">
-        <v>48.50968523333334</v>
+        <v>48.10180253333333</v>
       </c>
       <c r="O5">
-        <v>11.642324456</v>
+        <v>11.544432608</v>
       </c>
       <c r="P5">
-        <v>36.86736077733333</v>
+        <v>36.55736992533333</v>
       </c>
       <c r="Q5">
-        <v>58.46736077733333</v>
+        <v>58.15736992533333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07866794269307267</v>
+        <v>0.07893003429895518</v>
       </c>
       <c r="T5">
-        <v>0.5542007326019179</v>
+        <v>0.5586199736035616</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.64349328318602</v>
+        <v>30.48261996238951</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07730195292699696</v>
+        <v>0.07714916144171345</v>
       </c>
       <c r="C6">
-        <v>787.5264586675722</v>
+        <v>782.9795813994801</v>
       </c>
       <c r="D6">
-        <v>730.8624586675722</v>
+        <v>734.4245813994801</v>
       </c>
       <c r="E6">
-        <v>-282.364</v>
+        <v>-274.255</v>
       </c>
       <c r="F6">
-        <v>32.43600000000001</v>
+        <v>40.54500000000001</v>
       </c>
       <c r="G6">
         <v>89.09999999999999</v>
@@ -1785,28 +1785,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M6">
-        <v>1.6315308</v>
+        <v>2.0394135</v>
       </c>
       <c r="N6">
-        <v>48.10180253333333</v>
+        <v>47.69391983333333</v>
       </c>
       <c r="O6">
-        <v>11.544432608</v>
+        <v>11.44654076</v>
       </c>
       <c r="P6">
-        <v>36.55736992533333</v>
+        <v>36.24737907333333</v>
       </c>
       <c r="Q6">
-        <v>58.15736992533333</v>
+        <v>57.84737907333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07893003429895518</v>
+        <v>0.07919764362285628</v>
       </c>
       <c r="T6">
-        <v>0.5586199736035616</v>
+        <v>0.5631322512578715</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.48261996238951</v>
+        <v>24.38609596991161</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07714916144171345</v>
+        <v>0.07699636995642994</v>
       </c>
       <c r="C7">
-        <v>782.9795813994801</v>
+        <v>778.4675967822784</v>
       </c>
       <c r="D7">
-        <v>734.4245813994801</v>
+        <v>738.0215967822784</v>
       </c>
       <c r="E7">
-        <v>-274.255</v>
+        <v>-266.146</v>
       </c>
       <c r="F7">
-        <v>40.54500000000001</v>
+        <v>48.65400000000001</v>
       </c>
       <c r="G7">
         <v>89.09999999999999</v>
@@ -1867,28 +1867,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M7">
-        <v>2.0394135</v>
+        <v>2.4472962</v>
       </c>
       <c r="N7">
-        <v>47.69391983333333</v>
+        <v>47.28603713333334</v>
       </c>
       <c r="O7">
-        <v>11.44654076</v>
+        <v>11.348648912</v>
       </c>
       <c r="P7">
-        <v>36.24737907333333</v>
+        <v>35.93738822133334</v>
       </c>
       <c r="Q7">
-        <v>57.84737907333333</v>
+        <v>57.53738822133333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07919764362285628</v>
+        <v>0.07947094676215952</v>
       </c>
       <c r="T7">
-        <v>0.5631322512578715</v>
+        <v>0.5677405348197199</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.38609596991161</v>
+        <v>20.32174664159301</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07699636995642994</v>
+        <v>0.07684357847114642</v>
       </c>
       <c r="C8">
-        <v>778.4675967822784</v>
+        <v>773.9910200239639</v>
       </c>
       <c r="D8">
-        <v>738.0215967822784</v>
+        <v>741.6540200239639</v>
       </c>
       <c r="E8">
-        <v>-266.146</v>
+        <v>-258.037</v>
       </c>
       <c r="F8">
-        <v>48.654</v>
+        <v>56.763</v>
       </c>
       <c r="G8">
         <v>89.09999999999999</v>
@@ -1949,28 +1949,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M8">
-        <v>2.4472962</v>
+        <v>2.8551789</v>
       </c>
       <c r="N8">
-        <v>47.28603713333334</v>
+        <v>46.87815443333334</v>
       </c>
       <c r="O8">
-        <v>11.348648912</v>
+        <v>11.250757064</v>
       </c>
       <c r="P8">
-        <v>35.93738822133334</v>
+        <v>35.62739736933334</v>
       </c>
       <c r="Q8">
-        <v>57.53738822133333</v>
+        <v>57.22739736933333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07947094676215952</v>
+        <v>0.07975012738832948</v>
       </c>
       <c r="T8">
-        <v>0.5677405348197199</v>
+        <v>0.5724479212538659</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.32174664159301</v>
+        <v>17.4186399785083</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07684357847114642</v>
+        <v>0.07669078698586292</v>
       </c>
       <c r="C9">
-        <v>773.9910200239639</v>
+        <v>769.5503765257845</v>
       </c>
       <c r="D9">
-        <v>741.6540200239639</v>
+        <v>745.3223765257845</v>
       </c>
       <c r="E9">
-        <v>-258.037</v>
+        <v>-249.928</v>
       </c>
       <c r="F9">
-        <v>56.76300000000001</v>
+        <v>64.87200000000001</v>
       </c>
       <c r="G9">
         <v>89.09999999999999</v>
@@ -2031,28 +2031,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M9">
-        <v>2.8551789</v>
+        <v>3.2630616</v>
       </c>
       <c r="N9">
-        <v>46.87815443333334</v>
+        <v>46.47027173333333</v>
       </c>
       <c r="O9">
-        <v>11.250757064</v>
+        <v>11.152865216</v>
       </c>
       <c r="P9">
-        <v>35.62739736933334</v>
+        <v>35.31740651733333</v>
       </c>
       <c r="Q9">
-        <v>57.22739736933333</v>
+        <v>56.91740651733333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07975012738832948</v>
+        <v>0.08003537715854664</v>
       </c>
       <c r="T9">
-        <v>0.5724479212538659</v>
+        <v>0.577257642175711</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.41863997850829</v>
+        <v>15.24130998119475</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07669078698586292</v>
+        <v>0.07653799550057939</v>
       </c>
       <c r="C10">
-        <v>769.5503765257845</v>
+        <v>765.1462021355829</v>
       </c>
       <c r="D10">
-        <v>745.3223765257845</v>
+        <v>749.0272021355829</v>
       </c>
       <c r="E10">
-        <v>-249.928</v>
+        <v>-241.819</v>
       </c>
       <c r="F10">
-        <v>64.87200000000001</v>
+        <v>72.98100000000001</v>
       </c>
       <c r="G10">
         <v>89.09999999999999</v>
@@ -2113,28 +2113,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M10">
-        <v>3.2630616</v>
+        <v>3.6709443</v>
       </c>
       <c r="N10">
-        <v>46.47027173333333</v>
+        <v>46.06238903333333</v>
       </c>
       <c r="O10">
-        <v>11.152865216</v>
+        <v>11.054973368</v>
       </c>
       <c r="P10">
-        <v>35.31740651733333</v>
+        <v>35.00741566533333</v>
       </c>
       <c r="Q10">
-        <v>56.91740651733333</v>
+        <v>56.60741566533333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08003537715854664</v>
+        <v>0.08032689615448285</v>
       </c>
       <c r="T10">
-        <v>0.577257642175711</v>
+        <v>0.5821730712496844</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.24130998119475</v>
+        <v>13.54783109439534</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07653799550057939</v>
+        <v>0.0764992040152959</v>
       </c>
       <c r="C11">
-        <v>765.1462021355829</v>
+        <v>757.9836722028231</v>
       </c>
       <c r="D11">
-        <v>749.0272021355829</v>
+        <v>749.9736722028231</v>
       </c>
       <c r="E11">
-        <v>-241.819</v>
+        <v>-233.71</v>
       </c>
       <c r="F11">
-        <v>72.98100000000001</v>
+        <v>81.09</v>
       </c>
       <c r="G11">
         <v>89.09999999999999</v>
@@ -2195,45 +2195,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M11">
-        <v>3.6709443</v>
+        <v>4.200462</v>
       </c>
       <c r="N11">
-        <v>46.06238903333333</v>
+        <v>45.53287133333333</v>
       </c>
       <c r="O11">
-        <v>11.054973368</v>
+        <v>10.92788912</v>
       </c>
       <c r="P11">
-        <v>35.00741566533333</v>
+        <v>34.60498221333333</v>
       </c>
       <c r="Q11">
-        <v>56.60741566533333</v>
+        <v>56.20498221333332</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08032689615448285</v>
+        <v>0.08062489335032877</v>
       </c>
       <c r="T11">
-        <v>0.5821730712496844</v>
+        <v>0.5871977320808575</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.54783109439534</v>
+        <v>11.83996744485091</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0764992040152959</v>
+        <v>0.07635781253001236</v>
       </c>
       <c r="C12">
-        <v>757.9836722028231</v>
+        <v>753.3448123292528</v>
       </c>
       <c r="D12">
-        <v>749.9736722028231</v>
+        <v>753.4438123292528</v>
       </c>
       <c r="E12">
-        <v>-233.71</v>
+        <v>-225.601</v>
       </c>
       <c r="F12">
-        <v>81.09000000000002</v>
+        <v>89.19900000000001</v>
       </c>
       <c r="G12">
         <v>89.09999999999999</v>
@@ -2277,28 +2277,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M12">
-        <v>4.200462000000001</v>
+        <v>4.620508200000001</v>
       </c>
       <c r="N12">
-        <v>45.53287133333333</v>
+        <v>45.11282513333333</v>
       </c>
       <c r="O12">
-        <v>10.92788912</v>
+        <v>10.827078032</v>
       </c>
       <c r="P12">
-        <v>34.60498221333333</v>
+        <v>34.28574710133333</v>
       </c>
       <c r="Q12">
-        <v>56.20498221333332</v>
+        <v>55.88574710133332</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08062489335032877</v>
+        <v>0.08092958711237344</v>
       </c>
       <c r="T12">
-        <v>0.5871977320808575</v>
+        <v>0.5923353066385735</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.83996744485091</v>
+        <v>10.76360676804628</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07635781253001236</v>
+        <v>0.07621642104472887</v>
       </c>
       <c r="C13">
-        <v>753.3448123292528</v>
+        <v>748.7382145200377</v>
       </c>
       <c r="D13">
-        <v>753.4438123292528</v>
+        <v>756.9462145200376</v>
       </c>
       <c r="E13">
-        <v>-225.601</v>
+        <v>-217.492</v>
       </c>
       <c r="F13">
-        <v>89.19900000000001</v>
+        <v>97.30800000000001</v>
       </c>
       <c r="G13">
         <v>89.09999999999999</v>
@@ -2359,28 +2359,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M13">
-        <v>4.620508200000001</v>
+        <v>5.0405544</v>
       </c>
       <c r="N13">
-        <v>45.11282513333333</v>
+        <v>44.69277893333334</v>
       </c>
       <c r="O13">
-        <v>10.827078032</v>
+        <v>10.726266944</v>
       </c>
       <c r="P13">
-        <v>34.28574710133333</v>
+        <v>33.96651198933333</v>
       </c>
       <c r="Q13">
-        <v>55.88574710133332</v>
+        <v>55.56651198933334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08092958711237344</v>
+        <v>0.08124120573264643</v>
       </c>
       <c r="T13">
-        <v>0.5923353066385735</v>
+        <v>0.5975896442544194</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.76360676804628</v>
+        <v>9.866639537375756</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07621642104472887</v>
+        <v>0.07624298955944533</v>
       </c>
       <c r="C14">
-        <v>748.7382145200377</v>
+        <v>739.9686047398851</v>
       </c>
       <c r="D14">
-        <v>756.9462145200376</v>
+        <v>756.2856047398851</v>
       </c>
       <c r="E14">
-        <v>-217.492</v>
+        <v>-209.383</v>
       </c>
       <c r="F14">
-        <v>97.30800000000001</v>
+        <v>105.417</v>
       </c>
       <c r="G14">
         <v>89.09999999999999</v>
@@ -2441,45 +2441,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M14">
-        <v>5.0405544</v>
+        <v>5.639809500000001</v>
       </c>
       <c r="N14">
-        <v>44.69277893333334</v>
+        <v>44.09352383333334</v>
       </c>
       <c r="O14">
-        <v>10.726266944</v>
+        <v>10.58244572</v>
       </c>
       <c r="P14">
-        <v>33.96651198933333</v>
+        <v>33.51107811333333</v>
       </c>
       <c r="Q14">
-        <v>55.56651198933334</v>
+        <v>55.11107811333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08124120573264643</v>
+        <v>0.08155998799936245</v>
       </c>
       <c r="T14">
-        <v>0.5975896442544194</v>
+        <v>0.6029647712407448</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.866639537375756</v>
+        <v>8.818264754037052</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07624298955944533</v>
+        <v>0.07611451807416184</v>
       </c>
       <c r="C15">
-        <v>739.9686047398851</v>
+        <v>735.0647071499503</v>
       </c>
       <c r="D15">
-        <v>756.2856047398851</v>
+        <v>759.4907071499504</v>
       </c>
       <c r="E15">
-        <v>-209.383</v>
+        <v>-201.274</v>
       </c>
       <c r="F15">
-        <v>105.417</v>
+        <v>113.526</v>
       </c>
       <c r="G15">
         <v>89.09999999999999</v>
@@ -2523,28 +2523,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M15">
-        <v>5.639809500000001</v>
+        <v>6.073641000000001</v>
       </c>
       <c r="N15">
-        <v>44.09352383333334</v>
+        <v>43.65969233333333</v>
       </c>
       <c r="O15">
-        <v>10.58244572</v>
+        <v>10.47832616</v>
       </c>
       <c r="P15">
-        <v>33.51107811333333</v>
+        <v>33.18136617333333</v>
       </c>
       <c r="Q15">
-        <v>55.11107811333333</v>
+        <v>54.78136617333332</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08155998799936245</v>
+        <v>0.08188618380716492</v>
       </c>
       <c r="T15">
-        <v>0.6029647712407448</v>
+        <v>0.6084649011802403</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.818264754037052</v>
+        <v>8.188388700177262</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07611451807416184</v>
+        <v>0.07598604658887832</v>
       </c>
       <c r="C16">
-        <v>735.0647071499503</v>
+        <v>730.1880913218654</v>
       </c>
       <c r="D16">
-        <v>759.4907071499504</v>
+        <v>762.7230913218654</v>
       </c>
       <c r="E16">
-        <v>-201.274</v>
+        <v>-193.165</v>
       </c>
       <c r="F16">
-        <v>113.526</v>
+        <v>121.635</v>
       </c>
       <c r="G16">
         <v>89.09999999999999</v>
@@ -2605,28 +2605,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M16">
-        <v>6.073641000000001</v>
+        <v>6.507472500000001</v>
       </c>
       <c r="N16">
-        <v>43.65969233333333</v>
+        <v>43.22586083333334</v>
       </c>
       <c r="O16">
-        <v>10.47832616</v>
+        <v>10.3742066</v>
       </c>
       <c r="P16">
-        <v>33.18136617333333</v>
+        <v>32.85165423333333</v>
       </c>
       <c r="Q16">
-        <v>54.78136617333332</v>
+        <v>54.45165423333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08188618380716492</v>
+        <v>0.08222005481044507</v>
       </c>
       <c r="T16">
-        <v>0.6084649011802403</v>
+        <v>0.6140944459418417</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.188388700177262</v>
+        <v>7.642496120165445</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07598604658887831</v>
+        <v>0.0759548551035948</v>
       </c>
       <c r="C17">
-        <v>730.1880913218657</v>
+        <v>722.8680344620873</v>
       </c>
       <c r="D17">
-        <v>762.7230913218657</v>
+        <v>763.5120344620873</v>
       </c>
       <c r="E17">
-        <v>-193.165</v>
+        <v>-185.056</v>
       </c>
       <c r="F17">
-        <v>121.635</v>
+        <v>129.744</v>
       </c>
       <c r="G17">
         <v>89.09999999999999</v>
@@ -2687,45 +2687,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M17">
-        <v>6.5074725</v>
+        <v>7.045099200000002</v>
       </c>
       <c r="N17">
-        <v>43.22586083333334</v>
+        <v>42.68823413333333</v>
       </c>
       <c r="O17">
-        <v>10.3742066</v>
+        <v>10.245176192</v>
       </c>
       <c r="P17">
-        <v>32.85165423333333</v>
+        <v>32.44305794133334</v>
       </c>
       <c r="Q17">
-        <v>54.45165423333333</v>
+        <v>54.04305794133333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08222005481044506</v>
+        <v>0.08256187512332713</v>
       </c>
       <c r="T17">
-        <v>0.6140944459418416</v>
+        <v>0.6198580274834812</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.642496120165446</v>
+        <v>7.059280773978785</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0759548551035948</v>
+        <v>0.07583246361831128</v>
       </c>
       <c r="C18">
-        <v>722.8680344620873</v>
+        <v>717.8705797924105</v>
       </c>
       <c r="D18">
-        <v>763.5120344620873</v>
+        <v>766.6235797924105</v>
       </c>
       <c r="E18">
-        <v>-185.056</v>
+        <v>-176.947</v>
       </c>
       <c r="F18">
-        <v>129.744</v>
+        <v>137.853</v>
       </c>
       <c r="G18">
         <v>89.09999999999999</v>
@@ -2769,28 +2769,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M18">
-        <v>7.045099200000002</v>
+        <v>7.485417900000003</v>
       </c>
       <c r="N18">
-        <v>42.68823413333333</v>
+        <v>42.24791543333333</v>
       </c>
       <c r="O18">
-        <v>10.245176192</v>
+        <v>10.139499704</v>
       </c>
       <c r="P18">
-        <v>32.44305794133334</v>
+        <v>32.10841572933333</v>
       </c>
       <c r="Q18">
-        <v>54.04305794133333</v>
+        <v>53.70841572933332</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08256187512332713</v>
+        <v>0.08291193207025455</v>
       </c>
       <c r="T18">
-        <v>0.6198580274834812</v>
+        <v>0.6257604905080517</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.059280773978785</v>
+        <v>6.644028963744739</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07583246361831128</v>
+        <v>0.07571007213302777</v>
       </c>
       <c r="C19">
-        <v>717.8705797924105</v>
+        <v>712.8985898994688</v>
       </c>
       <c r="D19">
-        <v>766.6235797924105</v>
+        <v>769.7605898994689</v>
       </c>
       <c r="E19">
-        <v>-176.947</v>
+        <v>-168.838</v>
       </c>
       <c r="F19">
-        <v>137.853</v>
+        <v>145.962</v>
       </c>
       <c r="G19">
         <v>89.09999999999999</v>
@@ -2851,28 +2851,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M19">
-        <v>7.485417900000003</v>
+        <v>7.925736600000002</v>
       </c>
       <c r="N19">
-        <v>42.24791543333333</v>
+        <v>41.80759673333333</v>
       </c>
       <c r="O19">
-        <v>10.139499704</v>
+        <v>10.033823216</v>
       </c>
       <c r="P19">
-        <v>32.10841572933333</v>
+        <v>31.77377351733333</v>
       </c>
       <c r="Q19">
-        <v>53.70841572933332</v>
+        <v>53.37377351733333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08291193207025455</v>
+        <v>0.08327052699149728</v>
       </c>
       <c r="T19">
-        <v>0.6257604905080517</v>
+        <v>0.6318069160454168</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.644028963744739</v>
+        <v>6.274916243536699</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07571007213302779</v>
+        <v>0.07573208064774427</v>
       </c>
       <c r="C20">
-        <v>712.8985898994686</v>
+        <v>704.2235989324407</v>
       </c>
       <c r="D20">
-        <v>769.7605898994685</v>
+        <v>769.1945989324407</v>
       </c>
       <c r="E20">
-        <v>-168.838</v>
+        <v>-160.729</v>
       </c>
       <c r="F20">
-        <v>145.962</v>
+        <v>154.071</v>
       </c>
       <c r="G20">
         <v>89.09999999999999</v>
@@ -2933,45 +2933,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M20">
-        <v>7.925736600000001</v>
+        <v>8.520126300000001</v>
       </c>
       <c r="N20">
-        <v>41.80759673333333</v>
+        <v>41.21320703333333</v>
       </c>
       <c r="O20">
-        <v>10.033823216</v>
+        <v>9.891169688</v>
       </c>
       <c r="P20">
-        <v>31.77377351733333</v>
+        <v>31.32203734533334</v>
       </c>
       <c r="Q20">
-        <v>53.37377351733333</v>
+        <v>52.92203734533334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08327052699149728</v>
+        <v>0.08363797610832624</v>
       </c>
       <c r="T20">
-        <v>0.6318069160454167</v>
+        <v>0.6380026360404943</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.274916243536699</v>
+        <v>5.837159166681992</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07573208064774427</v>
+        <v>0.07561728916246074</v>
       </c>
       <c r="C21">
-        <v>704.2235989324407</v>
+        <v>699.0758671417144</v>
       </c>
       <c r="D21">
-        <v>769.1945989324407</v>
+        <v>772.1558671417145</v>
       </c>
       <c r="E21">
-        <v>-160.729</v>
+        <v>-152.62</v>
       </c>
       <c r="F21">
-        <v>154.071</v>
+        <v>162.18</v>
       </c>
       <c r="G21">
         <v>89.09999999999999</v>
@@ -3015,28 +3015,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M21">
-        <v>8.520126300000001</v>
+        <v>8.968554000000003</v>
       </c>
       <c r="N21">
-        <v>41.21320703333333</v>
+        <v>40.76477933333333</v>
       </c>
       <c r="O21">
-        <v>9.891169688</v>
+        <v>9.783547039999998</v>
       </c>
       <c r="P21">
-        <v>31.32203734533334</v>
+        <v>30.98123229333333</v>
       </c>
       <c r="Q21">
-        <v>52.92203734533334</v>
+        <v>52.58123229333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08363797610832624</v>
+        <v>0.08401461145307593</v>
       </c>
       <c r="T21">
-        <v>0.6380026360404943</v>
+        <v>0.644353249035449</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.837159166681992</v>
+        <v>5.545301208347891</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07561728916246074</v>
+        <v>0.07550249767717723</v>
       </c>
       <c r="C22">
-        <v>699.0758671417144</v>
+        <v>693.9510242258402</v>
       </c>
       <c r="D22">
-        <v>772.1558671417145</v>
+        <v>775.1400242258403</v>
       </c>
       <c r="E22">
-        <v>-152.62</v>
+        <v>-144.511</v>
       </c>
       <c r="F22">
-        <v>162.18</v>
+        <v>170.289</v>
       </c>
       <c r="G22">
         <v>89.09999999999999</v>
@@ -3097,28 +3097,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M22">
-        <v>8.968554000000003</v>
+        <v>9.416981700000003</v>
       </c>
       <c r="N22">
-        <v>40.76477933333333</v>
+        <v>40.31635163333333</v>
       </c>
       <c r="O22">
-        <v>9.783547039999998</v>
+        <v>9.675924391999999</v>
       </c>
       <c r="P22">
-        <v>30.98123229333333</v>
+        <v>30.64042724133333</v>
       </c>
       <c r="Q22">
-        <v>52.58123229333333</v>
+        <v>52.24042724133334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08401461145307593</v>
+        <v>0.08440078186984459</v>
       </c>
       <c r="T22">
-        <v>0.644353249035449</v>
+        <v>0.6508646370429342</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.545301208347891</v>
+        <v>5.281239246045612</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07550249767717723</v>
+        <v>0.07538770619189372</v>
       </c>
       <c r="C23">
-        <v>693.9510242258403</v>
+        <v>688.8493365908643</v>
       </c>
       <c r="D23">
-        <v>775.1400242258403</v>
+        <v>778.1473365908643</v>
       </c>
       <c r="E23">
-        <v>-144.511</v>
+        <v>-136.402</v>
       </c>
       <c r="F23">
-        <v>170.289</v>
+        <v>178.398</v>
       </c>
       <c r="G23">
         <v>89.09999999999999</v>
@@ -3179,28 +3179,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M23">
-        <v>9.416981700000001</v>
+        <v>9.865409400000003</v>
       </c>
       <c r="N23">
-        <v>40.31635163333333</v>
+        <v>39.86792393333333</v>
       </c>
       <c r="O23">
-        <v>9.675924391999999</v>
+        <v>9.568301743999999</v>
       </c>
       <c r="P23">
-        <v>30.64042724133333</v>
+        <v>30.29962218933333</v>
       </c>
       <c r="Q23">
-        <v>52.24042724133334</v>
+        <v>51.89962218933333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08440078186984459</v>
+        <v>0.08479685409217143</v>
       </c>
       <c r="T23">
-        <v>0.6508646370429342</v>
+        <v>0.6575429837172779</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.281239246045613</v>
+        <v>5.041182916679902</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07538770619189372</v>
+        <v>0.0752729147066102</v>
       </c>
       <c r="C24">
-        <v>688.8493365908643</v>
+        <v>683.77107479324</v>
       </c>
       <c r="D24">
-        <v>778.1473365908643</v>
+        <v>781.1780747932401</v>
       </c>
       <c r="E24">
-        <v>-136.402</v>
+        <v>-128.293</v>
       </c>
       <c r="F24">
-        <v>178.398</v>
+        <v>186.507</v>
       </c>
       <c r="G24">
         <v>89.09999999999999</v>
@@ -3261,28 +3261,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M24">
-        <v>9.865409400000003</v>
+        <v>10.3138371</v>
       </c>
       <c r="N24">
-        <v>39.86792393333333</v>
+        <v>39.41949623333333</v>
       </c>
       <c r="O24">
-        <v>9.568301743999999</v>
+        <v>9.460679096</v>
       </c>
       <c r="P24">
-        <v>30.29962218933333</v>
+        <v>29.95881713733333</v>
       </c>
       <c r="Q24">
-        <v>51.89962218933333</v>
+        <v>51.55881713733334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08479685409217143</v>
+        <v>0.08520321390468857</v>
       </c>
       <c r="T24">
-        <v>0.6575429837172779</v>
+        <v>0.6643947939416046</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.041182916679902</v>
+        <v>4.822001050737297</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0752729147066102</v>
+        <v>0.07515812322132669</v>
       </c>
       <c r="C25">
-        <v>683.77107479324</v>
+        <v>678.7165136209674</v>
       </c>
       <c r="D25">
-        <v>781.1780747932401</v>
+        <v>784.2325136209674</v>
       </c>
       <c r="E25">
-        <v>-128.293</v>
+        <v>-120.184</v>
       </c>
       <c r="F25">
-        <v>186.507</v>
+        <v>194.616</v>
       </c>
       <c r="G25">
         <v>89.09999999999999</v>
@@ -3343,28 +3343,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M25">
-        <v>10.3138371</v>
+        <v>10.7622648</v>
       </c>
       <c r="N25">
-        <v>39.41949623333333</v>
+        <v>38.97106853333333</v>
       </c>
       <c r="O25">
-        <v>9.460679096</v>
+        <v>9.353056447999998</v>
       </c>
       <c r="P25">
-        <v>29.95881713733333</v>
+        <v>29.61801208533333</v>
       </c>
       <c r="Q25">
-        <v>51.55881713733334</v>
+        <v>51.21801208533333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08520321390468857</v>
+        <v>0.08562026739648247</v>
       </c>
       <c r="T25">
-        <v>0.6643947939416046</v>
+        <v>0.6714269149613082</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.822001050737297</v>
+        <v>4.62108434028991</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07515812322132667</v>
+        <v>0.07551833173604318</v>
       </c>
       <c r="C26">
-        <v>678.7165136209679</v>
+        <v>661.1020261853729</v>
       </c>
       <c r="D26">
-        <v>784.2325136209679</v>
+        <v>774.7270261853729</v>
       </c>
       <c r="E26">
-        <v>-120.184</v>
+        <v>-112.075</v>
       </c>
       <c r="F26">
-        <v>194.616</v>
+        <v>202.725</v>
       </c>
       <c r="G26">
         <v>89.09999999999999</v>
@@ -3425,45 +3425,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M26">
-        <v>10.7622648</v>
+        <v>11.717505</v>
       </c>
       <c r="N26">
-        <v>38.97106853333334</v>
+        <v>38.01582833333333</v>
       </c>
       <c r="O26">
-        <v>9.353056448</v>
+        <v>9.123798799999999</v>
       </c>
       <c r="P26">
-        <v>29.61801208533334</v>
+        <v>28.89202953333333</v>
       </c>
       <c r="Q26">
-        <v>51.21801208533333</v>
+        <v>50.49202953333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08562026739648247</v>
+        <v>0.08604844231472422</v>
       </c>
       <c r="T26">
-        <v>0.6714269149613082</v>
+        <v>0.678646559208204</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.621084340289912</v>
+        <v>4.244362032133404</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07551833173604318</v>
+        <v>0.07542254025075966</v>
       </c>
       <c r="C27">
-        <v>661.1020261853729</v>
+        <v>655.4982891337684</v>
       </c>
       <c r="D27">
-        <v>774.7270261853729</v>
+        <v>777.2322891337684</v>
       </c>
       <c r="E27">
-        <v>-112.075</v>
+        <v>-103.966</v>
       </c>
       <c r="F27">
-        <v>202.725</v>
+        <v>210.834</v>
       </c>
       <c r="G27">
         <v>89.09999999999999</v>
@@ -3507,28 +3507,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M27">
-        <v>11.717505</v>
+        <v>12.1862052</v>
       </c>
       <c r="N27">
-        <v>38.01582833333333</v>
+        <v>37.54712813333333</v>
       </c>
       <c r="O27">
-        <v>9.123798799999999</v>
+        <v>9.011310751999998</v>
       </c>
       <c r="P27">
-        <v>28.89202953333333</v>
+        <v>28.53581738133333</v>
       </c>
       <c r="Q27">
-        <v>50.49202953333333</v>
+        <v>50.13581738133333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08604844231472422</v>
+        <v>0.08648818952805358</v>
       </c>
       <c r="T27">
-        <v>0.678646559208204</v>
+        <v>0.6860613289752862</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.244362032133404</v>
+        <v>4.081117338589811</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07542254025075966</v>
+        <v>0.07604494876547613</v>
       </c>
       <c r="C28">
-        <v>655.4982891337684</v>
+        <v>631.3946845992873</v>
       </c>
       <c r="D28">
-        <v>777.2322891337684</v>
+        <v>761.2376845992874</v>
       </c>
       <c r="E28">
-        <v>-103.966</v>
+        <v>-95.85699999999997</v>
       </c>
       <c r="F28">
-        <v>210.834</v>
+        <v>218.943</v>
       </c>
       <c r="G28">
         <v>89.09999999999999</v>
@@ -3589,45 +3589,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M28">
-        <v>12.1862052</v>
+        <v>13.4212059</v>
       </c>
       <c r="N28">
-        <v>37.54712813333333</v>
+        <v>36.31212743333333</v>
       </c>
       <c r="O28">
-        <v>9.011310751999998</v>
+        <v>8.714910583999998</v>
       </c>
       <c r="P28">
-        <v>28.53581738133333</v>
+        <v>27.59721684933333</v>
       </c>
       <c r="Q28">
-        <v>50.13581738133333</v>
+        <v>49.19721684933333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08648818952805358</v>
+        <v>0.08693998461024127</v>
       </c>
       <c r="T28">
-        <v>0.6860613289752862</v>
+        <v>0.6936792431195486</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.081117338589811</v>
+        <v>3.705578597325097</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07604494876547613</v>
+        <v>0.07597575728019261</v>
       </c>
       <c r="C29">
-        <v>631.3946845992873</v>
+        <v>625.031164109947</v>
       </c>
       <c r="D29">
-        <v>761.2376845992874</v>
+        <v>762.983164109947</v>
       </c>
       <c r="E29">
-        <v>-95.85699999999997</v>
+        <v>-87.74799999999996</v>
       </c>
       <c r="F29">
-        <v>218.943</v>
+        <v>227.052</v>
       </c>
       <c r="G29">
         <v>89.09999999999999</v>
@@ -3671,28 +3671,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M29">
-        <v>13.4212059</v>
+        <v>13.9182876</v>
       </c>
       <c r="N29">
-        <v>36.31212743333333</v>
+        <v>35.81504573333333</v>
       </c>
       <c r="O29">
-        <v>8.714910583999998</v>
+        <v>8.595610976</v>
       </c>
       <c r="P29">
-        <v>27.59721684933333</v>
+        <v>27.21943475733334</v>
       </c>
       <c r="Q29">
-        <v>49.19721684933333</v>
+        <v>48.81943475733333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08693998461024127</v>
+        <v>0.08740432955582308</v>
       </c>
       <c r="T29">
-        <v>0.6936792431195486</v>
+        <v>0.7015087659900406</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.705578597325097</v>
+        <v>3.573236504563487</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07597575728019261</v>
+        <v>0.0765236857949091</v>
       </c>
       <c r="C30">
-        <v>625.031164109947</v>
+        <v>603.3150651877945</v>
       </c>
       <c r="D30">
-        <v>762.983164109947</v>
+        <v>749.3760651877946</v>
       </c>
       <c r="E30">
-        <v>-87.74799999999996</v>
+        <v>-79.63899999999995</v>
       </c>
       <c r="F30">
-        <v>227.052</v>
+        <v>235.1610000000001</v>
       </c>
       <c r="G30">
         <v>89.09999999999999</v>
@@ -3753,45 +3753,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M30">
-        <v>13.9182876</v>
+        <v>15.0738201</v>
       </c>
       <c r="N30">
-        <v>35.81504573333333</v>
+        <v>34.65951323333333</v>
       </c>
       <c r="O30">
-        <v>8.595610976</v>
+        <v>8.318283175999998</v>
       </c>
       <c r="P30">
-        <v>27.21943475733334</v>
+        <v>26.34123005733333</v>
       </c>
       <c r="Q30">
-        <v>48.81943475733333</v>
+        <v>47.94123005733333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08740432955582308</v>
+        <v>0.08788175464071706</v>
       </c>
       <c r="T30">
-        <v>0.7015087659900406</v>
+        <v>0.7095588388005466</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.573236504563487</v>
+        <v>3.299318487510231</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0765236857949091</v>
+        <v>0.0764757743096256</v>
       </c>
       <c r="C31">
-        <v>603.3150651877945</v>
+        <v>596.3764910735982</v>
       </c>
       <c r="D31">
-        <v>749.3760651877946</v>
+        <v>750.5464910735982</v>
       </c>
       <c r="E31">
-        <v>-79.63900000000001</v>
+        <v>-71.53</v>
       </c>
       <c r="F31">
-        <v>235.161</v>
+        <v>243.27</v>
       </c>
       <c r="G31">
         <v>89.09999999999999</v>
@@ -3835,28 +3835,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M31">
-        <v>15.0738201</v>
+        <v>15.593607</v>
       </c>
       <c r="N31">
-        <v>34.65951323333334</v>
+        <v>34.13972633333333</v>
       </c>
       <c r="O31">
-        <v>8.318283176</v>
+        <v>8.193534319999998</v>
       </c>
       <c r="P31">
-        <v>26.34123005733333</v>
+        <v>25.94619201333333</v>
       </c>
       <c r="Q31">
-        <v>47.94123005733333</v>
+        <v>47.54619201333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08788175464071706</v>
+        <v>0.08837282044232228</v>
       </c>
       <c r="T31">
-        <v>0.7095588388005466</v>
+        <v>0.7178389136913526</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.299318487510232</v>
+        <v>3.189341204593223</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0764757743096256</v>
+        <v>0.07642786282434207</v>
       </c>
       <c r="C32">
-        <v>596.3764910735982</v>
+        <v>589.4415787782453</v>
       </c>
       <c r="D32">
-        <v>750.5464910735982</v>
+        <v>751.7205787782453</v>
       </c>
       <c r="E32">
-        <v>-71.53</v>
+        <v>-63.42099999999999</v>
       </c>
       <c r="F32">
-        <v>243.27</v>
+        <v>251.379</v>
       </c>
       <c r="G32">
         <v>89.09999999999999</v>
@@ -3917,28 +3917,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M32">
-        <v>15.593607</v>
+        <v>16.1133939</v>
       </c>
       <c r="N32">
-        <v>34.13972633333333</v>
+        <v>33.61993943333333</v>
       </c>
       <c r="O32">
-        <v>8.193534319999998</v>
+        <v>8.068785463999999</v>
       </c>
       <c r="P32">
-        <v>25.94619201333333</v>
+        <v>25.55115396933333</v>
       </c>
       <c r="Q32">
-        <v>47.54619201333333</v>
+        <v>47.15115396933332</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08837282044232228</v>
+        <v>0.08887812003527837</v>
       </c>
       <c r="T32">
-        <v>0.7178389136913526</v>
+        <v>0.7263589907529067</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.189341204593223</v>
+        <v>3.086459230251507</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07642786282434207</v>
+        <v>0.07827691133905856</v>
       </c>
       <c r="C33">
-        <v>589.4415787782453</v>
+        <v>538.5339331447215</v>
       </c>
       <c r="D33">
-        <v>751.7205787782453</v>
+        <v>708.9219331447215</v>
       </c>
       <c r="E33">
-        <v>-63.42099999999999</v>
+        <v>-55.31199999999995</v>
       </c>
       <c r="F33">
-        <v>251.379</v>
+        <v>259.4880000000001</v>
       </c>
       <c r="G33">
         <v>89.09999999999999</v>
@@ -3999,45 +3999,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M33">
-        <v>16.1133939</v>
+        <v>18.65718720000001</v>
       </c>
       <c r="N33">
-        <v>33.61993943333333</v>
+        <v>31.07614613333333</v>
       </c>
       <c r="O33">
-        <v>8.068785463999999</v>
+        <v>7.458275071999998</v>
       </c>
       <c r="P33">
-        <v>25.55115396933333</v>
+        <v>23.61787106133333</v>
       </c>
       <c r="Q33">
-        <v>47.15115396933332</v>
+        <v>45.21787106133333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08887812003527837</v>
+        <v>0.08939828138096848</v>
       </c>
       <c r="T33">
-        <v>0.7263589907529067</v>
+        <v>0.7351296583162711</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.086459230251507</v>
+        <v>2.665639402135243</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07827691133905856</v>
+        <v>0.07828827985377504</v>
       </c>
       <c r="C34">
-        <v>538.5339331447215</v>
+        <v>530.1768624722802</v>
       </c>
       <c r="D34">
-        <v>708.9219331447215</v>
+        <v>708.6738624722801</v>
       </c>
       <c r="E34">
-        <v>-55.31199999999995</v>
+        <v>-47.20299999999997</v>
       </c>
       <c r="F34">
-        <v>259.4880000000001</v>
+        <v>267.597</v>
       </c>
       <c r="G34">
         <v>89.09999999999999</v>
@@ -4081,28 +4081,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M34">
-        <v>18.65718720000001</v>
+        <v>19.2402243</v>
       </c>
       <c r="N34">
-        <v>31.07614613333333</v>
+        <v>30.49310903333333</v>
       </c>
       <c r="O34">
-        <v>7.458275071999998</v>
+        <v>7.318346167999999</v>
       </c>
       <c r="P34">
-        <v>23.61787106133333</v>
+        <v>23.17476286533333</v>
       </c>
       <c r="Q34">
-        <v>45.21787106133333</v>
+        <v>44.77476286533333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08939828138096848</v>
+        <v>0.08993396993100754</v>
       </c>
       <c r="T34">
-        <v>0.7351296583162711</v>
+        <v>0.7441621368516762</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.665639402135243</v>
+        <v>2.584862450555388</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07828827985377504</v>
+        <v>0.07829964836849153</v>
       </c>
       <c r="C35">
-        <v>530.1768624722802</v>
+        <v>521.8199653521833</v>
       </c>
       <c r="D35">
-        <v>708.6738624722801</v>
+        <v>708.4259653521833</v>
       </c>
       <c r="E35">
-        <v>-47.20299999999997</v>
+        <v>-39.09399999999994</v>
       </c>
       <c r="F35">
-        <v>267.597</v>
+        <v>275.7060000000001</v>
       </c>
       <c r="G35">
         <v>89.09999999999999</v>
@@ -4163,28 +4163,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M35">
-        <v>19.2402243</v>
+        <v>19.82326140000001</v>
       </c>
       <c r="N35">
-        <v>30.49310903333333</v>
+        <v>29.91007193333333</v>
       </c>
       <c r="O35">
-        <v>7.318346167999999</v>
+        <v>7.178417263999998</v>
       </c>
       <c r="P35">
-        <v>23.17476286533333</v>
+        <v>22.73165466933333</v>
       </c>
       <c r="Q35">
-        <v>44.77476286533333</v>
+        <v>44.33165466933333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08993396993100754</v>
+        <v>0.09048589146741141</v>
       </c>
       <c r="T35">
-        <v>0.7441621368516762</v>
+        <v>0.7534683268578513</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.584862450555388</v>
+        <v>2.508837084362582</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07829964836849153</v>
+        <v>0.07934841688320803</v>
       </c>
       <c r="C36">
-        <v>521.8199653521833</v>
+        <v>491.5646193694347</v>
       </c>
       <c r="D36">
-        <v>708.4259653521833</v>
+        <v>686.2796193694347</v>
       </c>
       <c r="E36">
-        <v>-39.09399999999994</v>
+        <v>-30.98499999999996</v>
       </c>
       <c r="F36">
-        <v>275.7060000000001</v>
+        <v>283.8150000000001</v>
       </c>
       <c r="G36">
         <v>89.09999999999999</v>
@@ -4245,45 +4245,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M36">
-        <v>19.82326140000001</v>
+        <v>21.51317700000001</v>
       </c>
       <c r="N36">
-        <v>29.91007193333333</v>
+        <v>28.22015633333333</v>
       </c>
       <c r="O36">
-        <v>7.178417263999998</v>
+        <v>6.772837519999999</v>
       </c>
       <c r="P36">
-        <v>22.73165466933333</v>
+        <v>21.44731881333333</v>
       </c>
       <c r="Q36">
-        <v>44.33165466933333</v>
+        <v>43.04731881333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09048589146741141</v>
+        <v>0.09105479520493542</v>
       </c>
       <c r="T36">
-        <v>0.7534683268578513</v>
+        <v>0.7630608611719086</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.508837084362582</v>
+        <v>2.31176145361205</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07934841688320803</v>
+        <v>0.07938942539792451</v>
       </c>
       <c r="C37">
-        <v>491.5646193694347</v>
+        <v>482.6177572286826</v>
       </c>
       <c r="D37">
-        <v>686.2796193694347</v>
+        <v>685.4417572286827</v>
       </c>
       <c r="E37">
-        <v>-30.98499999999996</v>
+        <v>-22.87599999999992</v>
       </c>
       <c r="F37">
-        <v>283.8150000000001</v>
+        <v>291.9240000000001</v>
       </c>
       <c r="G37">
         <v>89.09999999999999</v>
@@ -4327,28 +4327,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M37">
-        <v>21.51317700000001</v>
+        <v>22.12783920000001</v>
       </c>
       <c r="N37">
-        <v>28.22015633333333</v>
+        <v>27.60549413333333</v>
       </c>
       <c r="O37">
-        <v>6.772837519999999</v>
+        <v>6.625318591999998</v>
       </c>
       <c r="P37">
-        <v>21.44731881333333</v>
+        <v>20.98017554133333</v>
       </c>
       <c r="Q37">
-        <v>43.04731881333333</v>
+        <v>42.58017554133333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09105479520493542</v>
+        <v>0.09164147718425705</v>
       </c>
       <c r="T37">
-        <v>0.7630608611719086</v>
+        <v>0.7729531621832804</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.31176145361205</v>
+        <v>2.247545857678382</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07938942539792451</v>
+        <v>0.07943043391264099</v>
       </c>
       <c r="C38">
-        <v>482.6177572286827</v>
+        <v>473.6729384443752</v>
       </c>
       <c r="D38">
-        <v>685.4417572286827</v>
+        <v>684.6059384443752</v>
       </c>
       <c r="E38">
-        <v>-22.87599999999998</v>
+        <v>-14.767</v>
       </c>
       <c r="F38">
-        <v>291.924</v>
+        <v>300.033</v>
       </c>
       <c r="G38">
         <v>89.09999999999999</v>
@@ -4409,28 +4409,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M38">
-        <v>22.1278392</v>
+        <v>22.7425014</v>
       </c>
       <c r="N38">
-        <v>27.60549413333333</v>
+        <v>26.99083193333333</v>
       </c>
       <c r="O38">
-        <v>6.625318591999999</v>
+        <v>6.477799664</v>
       </c>
       <c r="P38">
-        <v>20.98017554133333</v>
+        <v>20.51303226933333</v>
       </c>
       <c r="Q38">
-        <v>42.58017554133333</v>
+        <v>42.11303226933333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09164147718425704</v>
+        <v>0.09224678398831904</v>
       </c>
       <c r="T38">
-        <v>0.7729531621832803</v>
+        <v>0.7831595044966001</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.247545857678382</v>
+        <v>2.186801375038426</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07943043391264099</v>
+        <v>0.07947144242735749</v>
       </c>
       <c r="C39">
-        <v>473.6729384443752</v>
+        <v>464.7301555506881</v>
       </c>
       <c r="D39">
-        <v>684.6059384443752</v>
+        <v>683.7721555506881</v>
       </c>
       <c r="E39">
-        <v>-14.767</v>
+        <v>-6.657999999999959</v>
       </c>
       <c r="F39">
-        <v>300.033</v>
+        <v>308.1420000000001</v>
       </c>
       <c r="G39">
         <v>89.09999999999999</v>
@@ -4491,28 +4491,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M39">
-        <v>22.7425014</v>
+        <v>23.35716360000001</v>
       </c>
       <c r="N39">
-        <v>26.99083193333333</v>
+        <v>26.37616973333333</v>
       </c>
       <c r="O39">
-        <v>6.477799664</v>
+        <v>6.330280735999998</v>
       </c>
       <c r="P39">
-        <v>20.51303226933333</v>
+        <v>20.04588899733333</v>
       </c>
       <c r="Q39">
-        <v>42.11303226933333</v>
+        <v>41.64588899733333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09224678398831904</v>
+        <v>0.09287161681831851</v>
       </c>
       <c r="T39">
-        <v>0.7831595044966001</v>
+        <v>0.7936950836587369</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.186801375038426</v>
+        <v>2.129253970432151</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07947144242735749</v>
+        <v>0.07951245094207397</v>
       </c>
       <c r="C40">
-        <v>464.7301555506881</v>
+        <v>455.7894011181253</v>
       </c>
       <c r="D40">
-        <v>683.7721555506881</v>
+        <v>682.9404011181254</v>
       </c>
       <c r="E40">
-        <v>-6.657999999999959</v>
+        <v>1.451000000000022</v>
       </c>
       <c r="F40">
-        <v>308.1420000000001</v>
+        <v>316.251</v>
       </c>
       <c r="G40">
         <v>89.09999999999999</v>
@@ -4573,28 +4573,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M40">
-        <v>23.35716360000001</v>
+        <v>23.9718258</v>
       </c>
       <c r="N40">
-        <v>26.37616973333333</v>
+        <v>25.76150753333333</v>
       </c>
       <c r="O40">
-        <v>6.330280735999998</v>
+        <v>6.182761807999999</v>
       </c>
       <c r="P40">
-        <v>20.04588899733333</v>
+        <v>19.57874572533333</v>
       </c>
       <c r="Q40">
-        <v>41.64588899733333</v>
+        <v>41.17874572533333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09287161681831851</v>
+        <v>0.09351693597061306</v>
       </c>
       <c r="T40">
-        <v>0.7936950836587369</v>
+        <v>0.8045760916458617</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.129253970432151</v>
+        <v>2.074657714780045</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07951245094207397</v>
+        <v>0.07955345945679046</v>
       </c>
       <c r="C41">
-        <v>455.7894011181253</v>
+        <v>446.8506677532953</v>
       </c>
       <c r="D41">
-        <v>682.9404011181254</v>
+        <v>682.1106677532954</v>
       </c>
       <c r="E41">
-        <v>1.451000000000022</v>
+        <v>9.560000000000059</v>
       </c>
       <c r="F41">
-        <v>316.251</v>
+        <v>324.3600000000001</v>
       </c>
       <c r="G41">
         <v>89.09999999999999</v>
@@ -4655,28 +4655,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M41">
-        <v>23.9718258</v>
+        <v>24.58648800000001</v>
       </c>
       <c r="N41">
-        <v>25.76150753333333</v>
+        <v>25.14684533333333</v>
       </c>
       <c r="O41">
-        <v>6.182761807999999</v>
+        <v>6.035242879999998</v>
       </c>
       <c r="P41">
-        <v>19.57874572533333</v>
+        <v>19.11160245333333</v>
       </c>
       <c r="Q41">
-        <v>41.17874572533333</v>
+        <v>40.71160245333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09351693597061306</v>
+        <v>0.09418376576131743</v>
       </c>
       <c r="T41">
-        <v>0.8045760916458617</v>
+        <v>0.815819799899224</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.074657714780045</v>
+        <v>2.022791271910544</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07955345945679046</v>
+        <v>0.08401918797150693</v>
       </c>
       <c r="C42">
-        <v>446.8506677532953</v>
+        <v>359.0403129927201</v>
       </c>
       <c r="D42">
-        <v>682.1106677532954</v>
+        <v>602.4093129927202</v>
       </c>
       <c r="E42">
-        <v>9.560000000000059</v>
+        <v>17.66900000000004</v>
       </c>
       <c r="F42">
-        <v>324.3600000000001</v>
+        <v>332.4690000000001</v>
       </c>
       <c r="G42">
         <v>89.09999999999999</v>
@@ -4737,45 +4737,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M42">
-        <v>24.58648800000001</v>
+        <v>29.92221</v>
       </c>
       <c r="N42">
-        <v>25.14684533333333</v>
+        <v>19.81112333333333</v>
       </c>
       <c r="O42">
-        <v>6.035242879999998</v>
+        <v>4.754669599999999</v>
       </c>
       <c r="P42">
-        <v>19.11160245333333</v>
+        <v>15.05645373333333</v>
       </c>
       <c r="Q42">
-        <v>40.71160245333333</v>
+        <v>36.65645373333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09418376576131743</v>
+        <v>0.09487319995170666</v>
       </c>
       <c r="T42">
-        <v>0.815819799899224</v>
+        <v>0.8274446508052425</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.022791271910544</v>
+        <v>1.662087570848989</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08401918797150693</v>
+        <v>0.08416811648622342</v>
       </c>
       <c r="C43">
-        <v>359.0403129927201</v>
+        <v>348.5930193142278</v>
       </c>
       <c r="D43">
-        <v>602.4093129927202</v>
+        <v>600.0710193142279</v>
       </c>
       <c r="E43">
-        <v>17.66900000000004</v>
+        <v>25.77800000000008</v>
       </c>
       <c r="F43">
-        <v>332.4690000000001</v>
+        <v>340.5780000000001</v>
       </c>
       <c r="G43">
         <v>89.09999999999999</v>
@@ -4819,28 +4819,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M43">
-        <v>29.92221</v>
+        <v>30.65202000000001</v>
       </c>
       <c r="N43">
-        <v>19.81112333333333</v>
+        <v>19.08131333333333</v>
       </c>
       <c r="O43">
-        <v>4.754669599999999</v>
+        <v>4.579515199999999</v>
       </c>
       <c r="P43">
-        <v>15.05645373333333</v>
+        <v>14.50179813333333</v>
       </c>
       <c r="Q43">
-        <v>36.65645373333333</v>
+        <v>36.10179813333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09487319995170666</v>
+        <v>0.09558640773486797</v>
       </c>
       <c r="T43">
-        <v>0.8274446508052425</v>
+        <v>0.8394703586390551</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.662087570848989</v>
+        <v>1.622514057257346</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08416811648622342</v>
+        <v>0.08431704500093989</v>
       </c>
       <c r="C44">
-        <v>348.5930193142279</v>
+        <v>338.1638079473204</v>
       </c>
       <c r="D44">
-        <v>600.0710193142279</v>
+        <v>597.7508079473204</v>
       </c>
       <c r="E44">
-        <v>25.77800000000002</v>
+        <v>33.887</v>
       </c>
       <c r="F44">
-        <v>340.578</v>
+        <v>348.687</v>
       </c>
       <c r="G44">
         <v>89.09999999999999</v>
@@ -4901,28 +4901,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M44">
-        <v>30.65202</v>
+        <v>31.38183</v>
       </c>
       <c r="N44">
-        <v>19.08131333333333</v>
+        <v>18.35150333333333</v>
       </c>
       <c r="O44">
-        <v>4.5795152</v>
+        <v>4.4043608</v>
       </c>
       <c r="P44">
-        <v>14.50179813333333</v>
+        <v>13.94714253333333</v>
       </c>
       <c r="Q44">
-        <v>36.10179813333333</v>
+        <v>35.54714253333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09558640773486796</v>
+        <v>0.09632464035252614</v>
       </c>
       <c r="T44">
-        <v>0.8394703586390549</v>
+        <v>0.8519180211337029</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.622514057257347</v>
+        <v>1.58478117220485</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08431704500093989</v>
+        <v>0.08446597351565639</v>
       </c>
       <c r="C45">
-        <v>338.1638079473204</v>
+        <v>327.7524699507836</v>
       </c>
       <c r="D45">
-        <v>597.7508079473204</v>
+        <v>595.4484699507836</v>
       </c>
       <c r="E45">
-        <v>33.887</v>
+        <v>41.99600000000004</v>
       </c>
       <c r="F45">
-        <v>348.687</v>
+        <v>356.796</v>
       </c>
       <c r="G45">
         <v>89.09999999999999</v>
@@ -4983,28 +4983,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M45">
-        <v>31.38183</v>
+        <v>32.11164</v>
       </c>
       <c r="N45">
-        <v>18.35150333333333</v>
+        <v>17.62169333333333</v>
       </c>
       <c r="O45">
-        <v>4.4043608</v>
+        <v>4.2292064</v>
       </c>
       <c r="P45">
-        <v>13.94714253333333</v>
+        <v>13.39248693333333</v>
       </c>
       <c r="Q45">
-        <v>35.54714253333333</v>
+        <v>34.99248693333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09632464035252614</v>
+        <v>0.09708923842081497</v>
       </c>
       <c r="T45">
-        <v>0.8519180211337029</v>
+        <v>0.8648102430031596</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.58478117220485</v>
+        <v>1.548763418291104</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08446597351565639</v>
+        <v>0.08461490203037289</v>
       </c>
       <c r="C46">
-        <v>327.7524699507836</v>
+        <v>317.3587995901425</v>
       </c>
       <c r="D46">
-        <v>595.4484699507836</v>
+        <v>593.1637995901425</v>
       </c>
       <c r="E46">
-        <v>41.99600000000004</v>
+        <v>50.10500000000002</v>
       </c>
       <c r="F46">
-        <v>356.796</v>
+        <v>364.905</v>
       </c>
       <c r="G46">
         <v>89.09999999999999</v>
@@ -5065,28 +5065,28 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M46">
-        <v>32.11164</v>
+        <v>32.84145</v>
       </c>
       <c r="N46">
-        <v>17.62169333333333</v>
+        <v>16.89188333333333</v>
       </c>
       <c r="O46">
-        <v>4.2292064</v>
+        <v>4.054052</v>
       </c>
       <c r="P46">
-        <v>13.39248693333333</v>
+        <v>12.83783133333333</v>
       </c>
       <c r="Q46">
-        <v>34.99248693333333</v>
+        <v>34.43783133333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09708923842081497</v>
+        <v>0.09788164005522342</v>
       </c>
       <c r="T46">
-        <v>0.8648102430031596</v>
+        <v>0.8781712729405967</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.548763418291104</v>
+        <v>1.51434645344019</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08461490203037289</v>
+        <v>0.1064337301409522</v>
       </c>
       <c r="C47">
-        <v>317.3587995901425</v>
+        <v>95.80195538544803</v>
       </c>
       <c r="D47">
-        <v>593.1637995901425</v>
+        <v>379.7159553854481</v>
       </c>
       <c r="E47">
-        <v>50.10500000000002</v>
+        <v>58.21400000000006</v>
       </c>
       <c r="F47">
-        <v>364.905</v>
+        <v>373.0140000000001</v>
       </c>
       <c r="G47">
         <v>89.09999999999999</v>
@@ -5147,45 +5147,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M47">
-        <v>32.84145</v>
+        <v>54.75845520000001</v>
       </c>
       <c r="N47">
-        <v>16.89188333333333</v>
+        <v>-5.02512186666668</v>
       </c>
       <c r="O47">
-        <v>4.054052</v>
+        <v>-1.206029248000003</v>
       </c>
       <c r="P47">
-        <v>12.83783133333333</v>
+        <v>-3.819092618666677</v>
       </c>
       <c r="Q47">
-        <v>34.43783133333334</v>
+        <v>17.78090738133332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09788164005522342</v>
+        <v>0.09930588457109421</v>
       </c>
       <c r="T47">
-        <v>0.8781712729405967</v>
+        <v>0.9021860815786262</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.24</v>
+        <v>0.217975469841231</v>
       </c>
       <c r="W47">
-        <v>0.0684</v>
+        <v>0.1148012010273073</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.51434645344019</v>
+        <v>0.9082311243384624</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1064337301409522</v>
+        <v>0.1074437301409522</v>
       </c>
       <c r="C48">
-        <v>95.80195538544803</v>
+        <v>81.47150976458158</v>
       </c>
       <c r="D48">
-        <v>379.7159553854481</v>
+        <v>373.4945097645817</v>
       </c>
       <c r="E48">
-        <v>58.21400000000006</v>
+        <v>66.32300000000004</v>
       </c>
       <c r="F48">
-        <v>373.0140000000001</v>
+        <v>381.123</v>
       </c>
       <c r="G48">
         <v>89.09999999999999</v>
@@ -5229,37 +5229,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M48">
-        <v>54.75845520000001</v>
+        <v>55.94885640000001</v>
       </c>
       <c r="N48">
-        <v>-5.02512186666668</v>
+        <v>-6.215523066666677</v>
       </c>
       <c r="O48">
-        <v>-1.206029248000003</v>
+        <v>-1.491725536000002</v>
       </c>
       <c r="P48">
-        <v>-3.819092618666677</v>
+        <v>-4.723797530666674</v>
       </c>
       <c r="Q48">
-        <v>17.78090738133332</v>
+        <v>16.87620246933332</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09930588457109421</v>
+        <v>0.1003154295630016</v>
       </c>
       <c r="T48">
-        <v>0.9021860815786262</v>
+        <v>0.9192084604763361</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.217975469841231</v>
+        <v>0.2133376938871622</v>
       </c>
       <c r="W48">
-        <v>0.1148012010273073</v>
+        <v>0.1154820265373646</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9082311243384624</v>
+        <v>0.888907057863176</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1074437301409522</v>
+        <v>0.1084537301409522</v>
       </c>
       <c r="C49">
-        <v>81.47150976458158</v>
+        <v>67.34164789389035</v>
       </c>
       <c r="D49">
-        <v>373.4945097645817</v>
+        <v>367.4736478938905</v>
       </c>
       <c r="E49">
-        <v>66.32300000000004</v>
+        <v>74.43200000000007</v>
       </c>
       <c r="F49">
-        <v>381.123</v>
+        <v>389.2320000000001</v>
       </c>
       <c r="G49">
         <v>89.09999999999999</v>
@@ -5311,37 +5311,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M49">
-        <v>55.94885640000001</v>
+        <v>57.13925760000001</v>
       </c>
       <c r="N49">
-        <v>-6.215523066666677</v>
+        <v>-7.40592426666668</v>
       </c>
       <c r="O49">
-        <v>-1.491725536000002</v>
+        <v>-1.777421824000003</v>
       </c>
       <c r="P49">
-        <v>-4.723797530666674</v>
+        <v>-5.628502442666678</v>
       </c>
       <c r="Q49">
-        <v>16.87620246933332</v>
+        <v>15.97149755733332</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1003154295630016</v>
+        <v>0.101363803208444</v>
       </c>
       <c r="T49">
-        <v>0.9192084604763361</v>
+        <v>0.9368855462547273</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2133376938871622</v>
+        <v>0.2088931585978463</v>
       </c>
       <c r="W49">
-        <v>0.1154820265373646</v>
+        <v>0.1161344843178362</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.888907057863176</v>
+        <v>0.8703881608243598</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1084537301409522</v>
+        <v>0.1094637301409522</v>
       </c>
       <c r="C50">
-        <v>67.34164789389064</v>
+        <v>53.40282322682964</v>
       </c>
       <c r="D50">
-        <v>367.4736478938906</v>
+        <v>361.6438232268297</v>
       </c>
       <c r="E50">
-        <v>74.43200000000002</v>
+        <v>82.54100000000005</v>
       </c>
       <c r="F50">
-        <v>389.232</v>
+        <v>397.3410000000001</v>
       </c>
       <c r="G50">
         <v>89.09999999999999</v>
@@ -5393,37 +5393,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M50">
-        <v>57.13925760000001</v>
+        <v>58.32965880000002</v>
       </c>
       <c r="N50">
-        <v>-7.405924266666673</v>
+        <v>-8.596325466666684</v>
       </c>
       <c r="O50">
-        <v>-1.777421824000001</v>
+        <v>-2.063118112000004</v>
       </c>
       <c r="P50">
-        <v>-5.628502442666672</v>
+        <v>-6.53320735466668</v>
       </c>
       <c r="Q50">
-        <v>15.97149755733333</v>
+        <v>15.06679264533332</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.101363803208444</v>
+        <v>0.1024532895458645</v>
       </c>
       <c r="T50">
-        <v>0.9368855462547271</v>
+        <v>0.9552558510832512</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2088931585978464</v>
+        <v>0.204630032912176</v>
       </c>
       <c r="W50">
-        <v>0.1161344843178362</v>
+        <v>0.1167603111684926</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8703881608243599</v>
+        <v>0.8526251371340667</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1094637301409522</v>
+        <v>0.1104737301409522</v>
       </c>
       <c r="C51">
-        <v>53.40282322682964</v>
+        <v>39.64608556482938</v>
       </c>
       <c r="D51">
-        <v>361.6438232268297</v>
+        <v>355.9960855648294</v>
       </c>
       <c r="E51">
-        <v>82.54100000000005</v>
+        <v>90.65000000000003</v>
       </c>
       <c r="F51">
-        <v>397.3410000000001</v>
+        <v>405.45</v>
       </c>
       <c r="G51">
         <v>89.09999999999999</v>
@@ -5475,37 +5475,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M51">
-        <v>58.32965880000002</v>
+        <v>59.52006000000002</v>
       </c>
       <c r="N51">
-        <v>-8.596325466666684</v>
+        <v>-9.786726666666681</v>
       </c>
       <c r="O51">
-        <v>-2.063118112000004</v>
+        <v>-2.348814400000003</v>
       </c>
       <c r="P51">
-        <v>-6.53320735466668</v>
+        <v>-7.437912266666677</v>
       </c>
       <c r="Q51">
-        <v>15.06679264533332</v>
+        <v>14.16208773333332</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1024532895458645</v>
+        <v>0.1035863553367818</v>
       </c>
       <c r="T51">
-        <v>0.9552558510832512</v>
+        <v>0.9743609681049163</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.204630032912176</v>
+        <v>0.2005374322539325</v>
       </c>
       <c r="W51">
-        <v>0.1167603111684926</v>
+        <v>0.1173611049451227</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8526251371340667</v>
+        <v>0.8355726343913854</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1104737301409522</v>
+        <v>0.1114837301409523</v>
       </c>
       <c r="C52">
-        <v>39.64608556482938</v>
+        <v>26.06303520793125</v>
       </c>
       <c r="D52">
-        <v>355.9960855648294</v>
+        <v>350.5220352079313</v>
       </c>
       <c r="E52">
-        <v>90.65000000000003</v>
+        <v>98.75900000000001</v>
       </c>
       <c r="F52">
-        <v>405.45</v>
+        <v>413.559</v>
       </c>
       <c r="G52">
         <v>89.09999999999999</v>
@@ -5557,37 +5557,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M52">
-        <v>59.52006000000002</v>
+        <v>60.71046120000001</v>
       </c>
       <c r="N52">
-        <v>-9.786726666666681</v>
+        <v>-10.97712786666668</v>
       </c>
       <c r="O52">
-        <v>-2.348814400000003</v>
+        <v>-2.634510688000002</v>
       </c>
       <c r="P52">
-        <v>-7.437912266666677</v>
+        <v>-8.342617178666675</v>
       </c>
       <c r="Q52">
-        <v>14.16208773333332</v>
+        <v>13.25738282133332</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1035863553367818</v>
+        <v>0.1047656687110018</v>
       </c>
       <c r="T52">
-        <v>0.9743609681049163</v>
+        <v>0.9942458858213432</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2005374322539325</v>
+        <v>0.1966053257391495</v>
       </c>
       <c r="W52">
-        <v>0.1173611049451227</v>
+        <v>0.1179383381814929</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8355726343913854</v>
+        <v>0.8191888572464563</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1114837301409523</v>
+        <v>0.1124937301409522</v>
       </c>
       <c r="C53">
-        <v>26.06303520793125</v>
+        <v>12.64578127143972</v>
       </c>
       <c r="D53">
-        <v>350.5220352079313</v>
+        <v>345.2137812714398</v>
       </c>
       <c r="E53">
-        <v>98.75900000000001</v>
+        <v>106.8680000000001</v>
       </c>
       <c r="F53">
-        <v>413.559</v>
+        <v>421.6680000000001</v>
       </c>
       <c r="G53">
         <v>89.09999999999999</v>
@@ -5639,37 +5639,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M53">
-        <v>60.71046120000001</v>
+        <v>61.90086240000002</v>
       </c>
       <c r="N53">
-        <v>-10.97712786666668</v>
+        <v>-12.16752906666668</v>
       </c>
       <c r="O53">
-        <v>-2.634510688000002</v>
+        <v>-2.920206976000003</v>
       </c>
       <c r="P53">
-        <v>-8.342617178666675</v>
+        <v>-9.247322090666678</v>
       </c>
       <c r="Q53">
-        <v>13.25738282133332</v>
+        <v>12.35267790933332</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1047656687110018</v>
+        <v>0.105994120142481</v>
       </c>
       <c r="T53">
-        <v>0.9942458858213432</v>
+        <v>1.014959341775955</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1966053257391495</v>
+        <v>0.1928244540903197</v>
       </c>
       <c r="W53">
-        <v>0.1179383381814929</v>
+        <v>0.1184933701395411</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8191888572464563</v>
+        <v>0.8034352253763322</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1124937301409522</v>
+        <v>0.1429896505831134</v>
       </c>
       <c r="C54">
-        <v>12.64578127143972</v>
+        <v>-103.7835177113063</v>
       </c>
       <c r="D54">
-        <v>345.2137812714398</v>
+        <v>236.8934822886938</v>
       </c>
       <c r="E54">
-        <v>106.8680000000001</v>
+        <v>114.977</v>
       </c>
       <c r="F54">
-        <v>421.6680000000001</v>
+        <v>429.777</v>
       </c>
       <c r="G54">
         <v>89.09999999999999</v>
@@ -5721,45 +5721,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M54">
-        <v>61.90086240000002</v>
+        <v>86.29922160000001</v>
       </c>
       <c r="N54">
-        <v>-12.16752906666668</v>
+        <v>-36.56588826666668</v>
       </c>
       <c r="O54">
-        <v>-2.920206976000003</v>
+        <v>-8.775813184000002</v>
       </c>
       <c r="P54">
-        <v>-9.247322090666678</v>
+        <v>-27.79007508266668</v>
       </c>
       <c r="Q54">
-        <v>12.35267790933332</v>
+        <v>-6.190075082666677</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.105994120142481</v>
+        <v>0.1091172300224512</v>
       </c>
       <c r="T54">
-        <v>1.014959341775955</v>
+        <v>1.067619461079393</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1928244540903197</v>
+        <v>0.1383094746245081</v>
       </c>
       <c r="W54">
-        <v>0.1184933701395411</v>
+        <v>0.1730274574953988</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8034352253763322</v>
+        <v>0.576289477602117</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1429896505831134</v>
+        <v>0.1445396505831134</v>
       </c>
       <c r="C55">
-        <v>-103.7835177113063</v>
+        <v>-115.6112355250625</v>
       </c>
       <c r="D55">
-        <v>236.8934822886938</v>
+        <v>233.1747644749376</v>
       </c>
       <c r="E55">
-        <v>114.977</v>
+        <v>123.0860000000001</v>
       </c>
       <c r="F55">
-        <v>429.777</v>
+        <v>437.8860000000001</v>
       </c>
       <c r="G55">
         <v>89.09999999999999</v>
@@ -5803,37 +5803,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M55">
-        <v>86.29922160000001</v>
+        <v>87.92750880000001</v>
       </c>
       <c r="N55">
-        <v>-36.56588826666668</v>
+        <v>-38.19417546666668</v>
       </c>
       <c r="O55">
-        <v>-8.775813184000002</v>
+        <v>-9.166602112000003</v>
       </c>
       <c r="P55">
-        <v>-27.79007508266668</v>
+        <v>-29.02757335466667</v>
       </c>
       <c r="Q55">
-        <v>-6.190075082666677</v>
+        <v>-7.427573354666677</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1091172300224512</v>
+        <v>0.1104936915446784</v>
       </c>
       <c r="T55">
-        <v>1.067619461079393</v>
+        <v>1.09082857979851</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1383094746245081</v>
+        <v>0.1357481880573876</v>
       </c>
       <c r="W55">
-        <v>0.1730274574953988</v>
+        <v>0.1735417638380766</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.576289477602117</v>
+        <v>0.5656174502391148</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1445396505831134</v>
+        <v>0.1460896505831134</v>
       </c>
       <c r="C56">
-        <v>-115.6112355250625</v>
+        <v>-127.3240060321361</v>
       </c>
       <c r="D56">
-        <v>233.1747644749376</v>
+        <v>229.570993967864</v>
       </c>
       <c r="E56">
-        <v>123.0860000000001</v>
+        <v>131.1950000000001</v>
       </c>
       <c r="F56">
-        <v>437.8860000000001</v>
+        <v>445.9950000000001</v>
       </c>
       <c r="G56">
         <v>89.09999999999999</v>
@@ -5885,37 +5885,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M56">
-        <v>87.92750880000001</v>
+        <v>89.55579600000002</v>
       </c>
       <c r="N56">
-        <v>-38.19417546666668</v>
+        <v>-39.82246266666668</v>
       </c>
       <c r="O56">
-        <v>-9.166602112000003</v>
+        <v>-9.557391040000002</v>
       </c>
       <c r="P56">
-        <v>-29.02757335466667</v>
+        <v>-30.26507162666668</v>
       </c>
       <c r="Q56">
-        <v>-7.427573354666677</v>
+        <v>-8.665071626666681</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1104936915446784</v>
+        <v>0.1119313291345602</v>
       </c>
       <c r="T56">
-        <v>1.09082857979851</v>
+        <v>1.115069214905144</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1357481880573876</v>
+        <v>0.1332800391836169</v>
       </c>
       <c r="W56">
-        <v>0.1735417638380766</v>
+        <v>0.1740373681319297</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5656174502391148</v>
+        <v>0.5553334965984036</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1460896505831134</v>
+        <v>0.1476396505831134</v>
       </c>
       <c r="C57">
-        <v>-127.3240060321361</v>
+        <v>-138.9270777283051</v>
       </c>
       <c r="D57">
-        <v>229.570993967864</v>
+        <v>226.0769222716951</v>
       </c>
       <c r="E57">
-        <v>131.1950000000001</v>
+        <v>139.3040000000001</v>
       </c>
       <c r="F57">
-        <v>445.9950000000001</v>
+        <v>454.1040000000001</v>
       </c>
       <c r="G57">
         <v>89.09999999999999</v>
@@ -5967,37 +5967,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M57">
-        <v>89.55579600000002</v>
+        <v>91.18408320000002</v>
       </c>
       <c r="N57">
-        <v>-39.82246266666668</v>
+        <v>-41.45074986666668</v>
       </c>
       <c r="O57">
-        <v>-9.557391040000002</v>
+        <v>-9.948179968000003</v>
       </c>
       <c r="P57">
-        <v>-30.26507162666668</v>
+        <v>-31.50256989866668</v>
       </c>
       <c r="Q57">
-        <v>-8.665071626666681</v>
+        <v>-9.90256989866668</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1119313291345602</v>
+        <v>0.1134343138876183</v>
       </c>
       <c r="T57">
-        <v>1.115069214905144</v>
+        <v>1.140411697062079</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1332800391836169</v>
+        <v>0.1309000384839094</v>
       </c>
       <c r="W57">
-        <v>0.1740373681319297</v>
+        <v>0.174515272272431</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5553334965984036</v>
+        <v>0.5454168270162892</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1476396505831134</v>
+        <v>0.1491896505831135</v>
       </c>
       <c r="C58">
-        <v>-138.9270777283051</v>
+        <v>-150.4253843711342</v>
       </c>
       <c r="D58">
-        <v>226.0769222716951</v>
+        <v>222.6876156288659</v>
       </c>
       <c r="E58">
-        <v>139.3040000000001</v>
+        <v>147.4130000000001</v>
       </c>
       <c r="F58">
-        <v>454.1040000000001</v>
+        <v>462.2130000000001</v>
       </c>
       <c r="G58">
         <v>89.09999999999999</v>
@@ -6049,37 +6049,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M58">
-        <v>91.18408320000002</v>
+        <v>92.81237040000002</v>
       </c>
       <c r="N58">
-        <v>-41.45074986666668</v>
+        <v>-43.07903706666669</v>
       </c>
       <c r="O58">
-        <v>-9.948179968000003</v>
+        <v>-10.338968896</v>
       </c>
       <c r="P58">
-        <v>-31.50256989866668</v>
+        <v>-32.74006817066668</v>
       </c>
       <c r="Q58">
-        <v>-9.90256989866668</v>
+        <v>-11.14006817066668</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1134343138876183</v>
+        <v>0.1150072049082606</v>
       </c>
       <c r="T58">
-        <v>1.140411697062079</v>
+        <v>1.166932899319337</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1309000384839094</v>
+        <v>0.1286035465806829</v>
       </c>
       <c r="W58">
-        <v>0.174515272272431</v>
+        <v>0.1749764078465989</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5454168270162892</v>
+        <v>0.5358481107528456</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1491896505831135</v>
+        <v>0.1507396505831134</v>
       </c>
       <c r="C59">
-        <v>-150.4253843711342</v>
+        <v>-161.8235682240132</v>
       </c>
       <c r="D59">
-        <v>222.6876156288659</v>
+        <v>219.3984317759869</v>
       </c>
       <c r="E59">
-        <v>147.4130000000001</v>
+        <v>155.5220000000001</v>
       </c>
       <c r="F59">
-        <v>462.2130000000001</v>
+        <v>470.3220000000001</v>
       </c>
       <c r="G59">
         <v>89.09999999999999</v>
@@ -6131,37 +6131,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M59">
-        <v>92.81237040000002</v>
+        <v>94.44065760000002</v>
       </c>
       <c r="N59">
-        <v>-43.07903706666669</v>
+        <v>-44.70732426666669</v>
       </c>
       <c r="O59">
-        <v>-10.338968896</v>
+        <v>-10.72975782400001</v>
       </c>
       <c r="P59">
-        <v>-32.74006817066668</v>
+        <v>-33.97756644266669</v>
       </c>
       <c r="Q59">
-        <v>-11.14006817066668</v>
+        <v>-12.37756644266669</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1150072049082606</v>
+        <v>0.1166549955013145</v>
       </c>
       <c r="T59">
-        <v>1.166932899319337</v>
+        <v>1.194717015969797</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1286035465806829</v>
+        <v>0.1263862440534298</v>
       </c>
       <c r="W59">
-        <v>0.1749764078465989</v>
+        <v>0.1754216421940713</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5358481107528456</v>
+        <v>0.5266093502226241</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1507396505831134</v>
+        <v>0.1522896505831134</v>
       </c>
       <c r="C60">
-        <v>-161.8235682240131</v>
+        <v>-173.1260012702355</v>
       </c>
       <c r="D60">
-        <v>219.3984317759869</v>
+        <v>216.2049987297646</v>
       </c>
       <c r="E60">
-        <v>155.522</v>
+        <v>163.631</v>
       </c>
       <c r="F60">
-        <v>470.322</v>
+        <v>478.431</v>
       </c>
       <c r="G60">
         <v>89.09999999999999</v>
@@ -6213,37 +6213,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M60">
-        <v>94.44065760000001</v>
+        <v>96.06894480000001</v>
       </c>
       <c r="N60">
-        <v>-44.70732426666667</v>
+        <v>-46.33561146666668</v>
       </c>
       <c r="O60">
-        <v>-10.729757824</v>
+        <v>-11.120546752</v>
       </c>
       <c r="P60">
-        <v>-33.97756644266667</v>
+        <v>-35.21506471466667</v>
       </c>
       <c r="Q60">
-        <v>-12.37756644266667</v>
+        <v>-13.61506471466668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1166549955013144</v>
+        <v>0.1183831661232977</v>
       </c>
       <c r="T60">
-        <v>1.194717015969797</v>
+        <v>1.223856455383694</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1263862440534298</v>
+        <v>0.1242441043237106</v>
       </c>
       <c r="W60">
-        <v>0.1754216421940713</v>
+        <v>0.1758517838517989</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5266093502226241</v>
+        <v>0.517683768015461</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1522896505831134</v>
+        <v>0.1538396505831134</v>
       </c>
       <c r="C61">
-        <v>-173.1260012702355</v>
+        <v>-184.3368046009796</v>
       </c>
       <c r="D61">
-        <v>216.2049987297646</v>
+        <v>213.1031953990204</v>
       </c>
       <c r="E61">
-        <v>163.631</v>
+        <v>171.74</v>
       </c>
       <c r="F61">
-        <v>478.431</v>
+        <v>486.54</v>
       </c>
       <c r="G61">
         <v>89.09999999999999</v>
@@ -6295,37 +6295,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M61">
-        <v>96.06894480000001</v>
+        <v>97.69723200000001</v>
       </c>
       <c r="N61">
-        <v>-46.33561146666668</v>
+        <v>-47.96389866666668</v>
       </c>
       <c r="O61">
-        <v>-11.120546752</v>
+        <v>-11.51133568</v>
       </c>
       <c r="P61">
-        <v>-35.21506471466667</v>
+        <v>-36.45256298666668</v>
       </c>
       <c r="Q61">
-        <v>-13.61506471466668</v>
+        <v>-14.85256298666668</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1183831661232977</v>
+        <v>0.1201977452763802</v>
       </c>
       <c r="T61">
-        <v>1.223856455383694</v>
+        <v>1.254452866768287</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1242441043237106</v>
+        <v>0.1221733692516488</v>
       </c>
       <c r="W61">
-        <v>0.1758517838517989</v>
+        <v>0.1762675874542689</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.517683768015461</v>
+        <v>0.5090557052152034</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1538396505831134</v>
+        <v>0.1553896505831134</v>
       </c>
       <c r="C62">
-        <v>-184.3368046009796</v>
+        <v>-195.4598661579874</v>
       </c>
       <c r="D62">
-        <v>213.1031953990204</v>
+        <v>210.0891338420126</v>
       </c>
       <c r="E62">
-        <v>171.74</v>
+        <v>179.849</v>
       </c>
       <c r="F62">
-        <v>486.54</v>
+        <v>494.6490000000001</v>
       </c>
       <c r="G62">
         <v>89.09999999999999</v>
@@ -6377,37 +6377,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M62">
-        <v>97.69723200000001</v>
+        <v>99.32551920000002</v>
       </c>
       <c r="N62">
-        <v>-47.96389866666668</v>
+        <v>-49.59218586666668</v>
       </c>
       <c r="O62">
-        <v>-11.51133568</v>
+        <v>-11.902124608</v>
       </c>
       <c r="P62">
-        <v>-36.45256298666668</v>
+        <v>-37.69006125866668</v>
       </c>
       <c r="Q62">
-        <v>-14.85256298666668</v>
+        <v>-16.09006125866668</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1201977452763802</v>
+        <v>0.1221053797706463</v>
       </c>
       <c r="T62">
-        <v>1.254452866768287</v>
+        <v>1.286618324890551</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1221733692516488</v>
+        <v>0.1201705271327693</v>
       </c>
       <c r="W62">
-        <v>0.1762675874542689</v>
+        <v>0.1766697581517399</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5090557052152034</v>
+        <v>0.5007105297198721</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1553896505831134</v>
+        <v>0.1789890599406845</v>
       </c>
       <c r="C63">
-        <v>-195.4598661579874</v>
+        <v>-240.7939916549556</v>
       </c>
       <c r="D63">
-        <v>210.0891338420126</v>
+        <v>172.8640083450444</v>
       </c>
       <c r="E63">
-        <v>179.849</v>
+        <v>187.958</v>
       </c>
       <c r="F63">
-        <v>494.6490000000001</v>
+        <v>502.758</v>
       </c>
       <c r="G63">
         <v>89.09999999999999</v>
@@ -6459,45 +6459,45 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M63">
-        <v>99.32551920000002</v>
+        <v>118.5503364</v>
       </c>
       <c r="N63">
-        <v>-49.59218586666668</v>
+        <v>-68.81700306666669</v>
       </c>
       <c r="O63">
-        <v>-11.902124608</v>
+        <v>-16.516080736</v>
       </c>
       <c r="P63">
-        <v>-37.69006125866668</v>
+        <v>-52.30092233066668</v>
       </c>
       <c r="Q63">
-        <v>-16.09006125866668</v>
+        <v>-30.70092233066668</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1221053797706463</v>
+        <v>0.1250329143897978</v>
       </c>
       <c r="T63">
-        <v>1.286618324890551</v>
+        <v>1.335980764328939</v>
       </c>
       <c r="U63">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1201705271327693</v>
+        <v>0.1006829703099855</v>
       </c>
       <c r="W63">
-        <v>0.1766697581517399</v>
+        <v>0.2120589556009054</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5007105297198721</v>
+        <v>0.4195123762916064</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1789890599406845</v>
+        <v>0.1808890599406845</v>
       </c>
       <c r="C64">
-        <v>-240.7939916549556</v>
+        <v>-251.334288578628</v>
       </c>
       <c r="D64">
-        <v>172.8640083450444</v>
+        <v>170.4327114213721</v>
       </c>
       <c r="E64">
-        <v>187.958</v>
+        <v>196.0670000000001</v>
       </c>
       <c r="F64">
-        <v>502.758</v>
+        <v>510.8670000000001</v>
       </c>
       <c r="G64">
         <v>89.09999999999999</v>
@@ -6541,37 +6541,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M64">
-        <v>118.5503364</v>
+        <v>120.4624386</v>
       </c>
       <c r="N64">
-        <v>-68.81700306666669</v>
+        <v>-70.72910526666669</v>
       </c>
       <c r="O64">
-        <v>-16.516080736</v>
+        <v>-16.974985264</v>
       </c>
       <c r="P64">
-        <v>-52.30092233066668</v>
+        <v>-53.75412000266669</v>
       </c>
       <c r="Q64">
-        <v>-30.70092233066668</v>
+        <v>-32.15412000266669</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1250329143897978</v>
+        <v>0.127174344508441</v>
       </c>
       <c r="T64">
-        <v>1.335980764328939</v>
+        <v>1.372088352554045</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1006829703099855</v>
+        <v>0.09908482792411274</v>
       </c>
       <c r="W64">
-        <v>0.2120589556009054</v>
+        <v>0.2124357975754942</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4195123762916064</v>
+        <v>0.4128534496838031</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1808890599406845</v>
+        <v>0.1827890599406845</v>
       </c>
       <c r="C65">
-        <v>-251.334288578628</v>
+        <v>-261.8071426837721</v>
       </c>
       <c r="D65">
-        <v>170.4327114213721</v>
+        <v>168.068857316228</v>
       </c>
       <c r="E65">
-        <v>196.0670000000001</v>
+        <v>204.1760000000001</v>
       </c>
       <c r="F65">
-        <v>510.8670000000001</v>
+        <v>518.9760000000001</v>
       </c>
       <c r="G65">
         <v>89.09999999999999</v>
@@ -6623,37 +6623,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M65">
-        <v>120.4624386</v>
+        <v>122.3745408</v>
       </c>
       <c r="N65">
-        <v>-70.72910526666669</v>
+        <v>-72.6412074666667</v>
       </c>
       <c r="O65">
-        <v>-16.974985264</v>
+        <v>-17.43388979200001</v>
       </c>
       <c r="P65">
-        <v>-53.75412000266669</v>
+        <v>-55.2073176746667</v>
       </c>
       <c r="Q65">
-        <v>-32.15412000266669</v>
+        <v>-33.6073176746667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.127174344508441</v>
+        <v>0.1294347429670088</v>
       </c>
       <c r="T65">
-        <v>1.372088352554045</v>
+        <v>1.410201917902769</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09908482792411274</v>
+        <v>0.09753662748779847</v>
       </c>
       <c r="W65">
-        <v>0.2124357975754942</v>
+        <v>0.2128008632383771</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4128534496838031</v>
+        <v>0.4064026145324937</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1827890599406845</v>
+        <v>0.1846890599406845</v>
       </c>
       <c r="C66">
-        <v>-261.8071426837721</v>
+        <v>-272.2153218202512</v>
       </c>
       <c r="D66">
-        <v>168.068857316228</v>
+        <v>165.7696781797489</v>
       </c>
       <c r="E66">
-        <v>204.1760000000001</v>
+        <v>212.285</v>
       </c>
       <c r="F66">
-        <v>518.9760000000001</v>
+        <v>527.085</v>
       </c>
       <c r="G66">
         <v>89.09999999999999</v>
@@ -6705,37 +6705,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M66">
-        <v>122.3745408</v>
+        <v>124.286643</v>
       </c>
       <c r="N66">
-        <v>-72.6412074666667</v>
+        <v>-74.55330966666668</v>
       </c>
       <c r="O66">
-        <v>-17.43388979200001</v>
+        <v>-17.89279432</v>
       </c>
       <c r="P66">
-        <v>-55.2073176746667</v>
+        <v>-56.66051534666667</v>
       </c>
       <c r="Q66">
-        <v>-33.6073176746667</v>
+        <v>-35.06051534666668</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1294347429670088</v>
+        <v>0.1318243070517805</v>
       </c>
       <c r="T66">
-        <v>1.410201917902769</v>
+        <v>1.450493401271419</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09753662748779847</v>
+        <v>0.09603606398798621</v>
       </c>
       <c r="W66">
-        <v>0.2128008632383771</v>
+        <v>0.2131546961116328</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4064026145324937</v>
+        <v>0.4001502666166092</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1846890599406845</v>
+        <v>0.1865890599406845</v>
       </c>
       <c r="C67">
-        <v>-272.2153218202512</v>
+        <v>-282.5614444253331</v>
       </c>
       <c r="D67">
-        <v>165.7696781797489</v>
+        <v>163.532555574667</v>
       </c>
       <c r="E67">
-        <v>212.285</v>
+        <v>220.3940000000001</v>
       </c>
       <c r="F67">
-        <v>527.085</v>
+        <v>535.1940000000001</v>
       </c>
       <c r="G67">
         <v>89.09999999999999</v>
@@ -6787,37 +6787,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M67">
-        <v>124.286643</v>
+        <v>126.1987452</v>
       </c>
       <c r="N67">
-        <v>-74.55330966666668</v>
+        <v>-76.46541186666668</v>
       </c>
       <c r="O67">
-        <v>-17.89279432</v>
+        <v>-18.35169884800001</v>
       </c>
       <c r="P67">
-        <v>-56.66051534666667</v>
+        <v>-58.11371301866668</v>
       </c>
       <c r="Q67">
-        <v>-35.06051534666668</v>
+        <v>-36.51371301866668</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1318243070517805</v>
+        <v>0.134354433729774</v>
       </c>
       <c r="T67">
-        <v>1.450493401271419</v>
+        <v>1.493154971897049</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09603606398798621</v>
+        <v>0.09458097210938035</v>
       </c>
       <c r="W67">
-        <v>0.2131546961116328</v>
+        <v>0.2134978067766081</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4001502666166092</v>
+        <v>0.3940873837890848</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1865890599406845</v>
+        <v>0.1884890599406845</v>
       </c>
       <c r="C68">
-        <v>-282.5614444253331</v>
+        <v>-292.8479894713305</v>
       </c>
       <c r="D68">
-        <v>163.532555574667</v>
+        <v>161.3550105286696</v>
       </c>
       <c r="E68">
-        <v>220.3940000000001</v>
+        <v>228.5030000000001</v>
       </c>
       <c r="F68">
-        <v>535.1940000000001</v>
+        <v>543.3030000000001</v>
       </c>
       <c r="G68">
         <v>89.09999999999999</v>
@@ -6869,37 +6869,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M68">
-        <v>126.1987452</v>
+        <v>128.1108474</v>
       </c>
       <c r="N68">
-        <v>-76.46541186666668</v>
+        <v>-78.37751406666671</v>
       </c>
       <c r="O68">
-        <v>-18.35169884800001</v>
+        <v>-18.81060337600001</v>
       </c>
       <c r="P68">
-        <v>-58.11371301866668</v>
+        <v>-59.5669106906667</v>
       </c>
       <c r="Q68">
-        <v>-36.51371301866668</v>
+        <v>-37.96691069066669</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.134354433729774</v>
+        <v>0.137037901418555</v>
       </c>
       <c r="T68">
-        <v>1.493154971897049</v>
+        <v>1.538402092257566</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09458097210938035</v>
+        <v>0.09316931580924033</v>
       </c>
       <c r="W68">
-        <v>0.2134978067766081</v>
+        <v>0.2138306753321811</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3940873837890848</v>
+        <v>0.3882054825385014</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1884890599406845</v>
+        <v>0.1903890599406845</v>
       </c>
       <c r="C69">
-        <v>-292.8479894713305</v>
+        <v>-303.0773056289309</v>
       </c>
       <c r="D69">
-        <v>161.3550105286696</v>
+        <v>159.2346943710693</v>
       </c>
       <c r="E69">
-        <v>228.5030000000001</v>
+        <v>236.6120000000001</v>
       </c>
       <c r="F69">
-        <v>543.3030000000001</v>
+        <v>551.4120000000001</v>
       </c>
       <c r="G69">
         <v>89.09999999999999</v>
@@ -6951,37 +6951,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M69">
-        <v>128.1108474</v>
+        <v>130.0229496</v>
       </c>
       <c r="N69">
-        <v>-78.37751406666671</v>
+        <v>-80.2896162666667</v>
       </c>
       <c r="O69">
-        <v>-18.81060337600001</v>
+        <v>-19.26950790400001</v>
       </c>
       <c r="P69">
-        <v>-59.5669106906667</v>
+        <v>-61.02010836266669</v>
       </c>
       <c r="Q69">
-        <v>-37.96691069066669</v>
+        <v>-39.4201083626667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.137037901418555</v>
+        <v>0.1398890858378849</v>
       </c>
       <c r="T69">
-        <v>1.538402092257566</v>
+        <v>1.586477157640615</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09316931580924033</v>
+        <v>0.09179917881204563</v>
       </c>
       <c r="W69">
-        <v>0.2138306753321811</v>
+        <v>0.2141537536361197</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3882054825385014</v>
+        <v>0.3824965783835235</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1903890599406845</v>
+        <v>0.1922890599406845</v>
       </c>
       <c r="C70">
-        <v>-303.0773056289309</v>
+        <v>-313.2516197174199</v>
       </c>
       <c r="D70">
-        <v>159.2346943710693</v>
+        <v>157.1693802825801</v>
       </c>
       <c r="E70">
-        <v>236.6120000000001</v>
+        <v>244.7210000000001</v>
       </c>
       <c r="F70">
-        <v>551.4120000000001</v>
+        <v>559.5210000000001</v>
       </c>
       <c r="G70">
         <v>89.09999999999999</v>
@@ -7033,37 +7033,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M70">
-        <v>130.0229496</v>
+        <v>131.9350518</v>
       </c>
       <c r="N70">
-        <v>-80.2896162666667</v>
+        <v>-82.20171846666669</v>
       </c>
       <c r="O70">
-        <v>-19.26950790400001</v>
+        <v>-19.72841243200001</v>
       </c>
       <c r="P70">
-        <v>-61.02010836266669</v>
+        <v>-62.47330603466668</v>
       </c>
       <c r="Q70">
-        <v>-39.4201083626667</v>
+        <v>-40.87330603466668</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1398890858378849</v>
+        <v>0.142924217639107</v>
       </c>
       <c r="T70">
-        <v>1.586477157640615</v>
+        <v>1.637653840145151</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09179917881204563</v>
+        <v>0.09046875593071164</v>
       </c>
       <c r="W70">
-        <v>0.2141537536361197</v>
+        <v>0.2144674673515382</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3824965783835235</v>
+        <v>0.3769531497112986</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1922890599406845</v>
+        <v>0.1941890599406846</v>
       </c>
       <c r="C71">
-        <v>-313.2516197174199</v>
+        <v>-323.3730445057182</v>
       </c>
       <c r="D71">
-        <v>157.1693802825801</v>
+        <v>155.1569554942819</v>
       </c>
       <c r="E71">
-        <v>244.7210000000001</v>
+        <v>252.8300000000001</v>
       </c>
       <c r="F71">
-        <v>559.5210000000001</v>
+        <v>567.6300000000001</v>
       </c>
       <c r="G71">
         <v>89.09999999999999</v>
@@ -7115,37 +7115,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M71">
-        <v>131.9350518</v>
+        <v>133.847154</v>
       </c>
       <c r="N71">
-        <v>-82.20171846666669</v>
+        <v>-84.11382066666668</v>
       </c>
       <c r="O71">
-        <v>-19.72841243200001</v>
+        <v>-20.18731696</v>
       </c>
       <c r="P71">
-        <v>-62.47330603466668</v>
+        <v>-63.92650370666668</v>
       </c>
       <c r="Q71">
-        <v>-40.87330603466668</v>
+        <v>-42.32650370666668</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.142924217639107</v>
+        <v>0.1461616915604106</v>
       </c>
       <c r="T71">
-        <v>1.637653840145151</v>
+        <v>1.692242301483323</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09046875593071164</v>
+        <v>0.08917634513170147</v>
       </c>
       <c r="W71">
-        <v>0.2144674673515382</v>
+        <v>0.2147722178179448</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3769531497112986</v>
+        <v>0.3715681047154229</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1941890599406846</v>
+        <v>0.1960890599406845</v>
       </c>
       <c r="C72">
-        <v>-323.3730445057182</v>
+        <v>-333.4435859216768</v>
       </c>
       <c r="D72">
-        <v>155.1569554942819</v>
+        <v>153.1954140783233</v>
       </c>
       <c r="E72">
-        <v>252.8300000000001</v>
+        <v>260.9390000000001</v>
       </c>
       <c r="F72">
-        <v>567.6300000000001</v>
+        <v>575.7390000000001</v>
       </c>
       <c r="G72">
         <v>89.09999999999999</v>
@@ -7197,37 +7197,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M72">
-        <v>133.847154</v>
+        <v>135.7592562</v>
       </c>
       <c r="N72">
-        <v>-84.11382066666668</v>
+        <v>-86.0259228666667</v>
       </c>
       <c r="O72">
-        <v>-20.18731696</v>
+        <v>-20.64622148800001</v>
       </c>
       <c r="P72">
-        <v>-63.92650370666668</v>
+        <v>-65.3797013786667</v>
       </c>
       <c r="Q72">
-        <v>-42.32650370666668</v>
+        <v>-43.7797013786667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1461616915604106</v>
+        <v>0.1496224395452523</v>
       </c>
       <c r="T72">
-        <v>1.692242301483323</v>
+        <v>1.750595484293093</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08917634513170147</v>
+        <v>0.08792034027069158</v>
       </c>
       <c r="W72">
-        <v>0.2147722178179448</v>
+        <v>0.2150683837641709</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3715681047154229</v>
+        <v>0.3663347511278816</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1960890599406845</v>
+        <v>0.1979890599406845</v>
       </c>
       <c r="C73">
-        <v>-333.4435859216767</v>
+        <v>-343.4651497213497</v>
       </c>
       <c r="D73">
-        <v>153.1954140783233</v>
+        <v>151.2828502786503</v>
       </c>
       <c r="E73">
-        <v>260.939</v>
+        <v>269.0480000000001</v>
       </c>
       <c r="F73">
-        <v>575.739</v>
+        <v>583.8480000000001</v>
       </c>
       <c r="G73">
         <v>89.09999999999999</v>
@@ -7279,37 +7279,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M73">
-        <v>135.7592562</v>
+        <v>137.6713584</v>
       </c>
       <c r="N73">
-        <v>-86.02592286666668</v>
+        <v>-87.9380250666667</v>
       </c>
       <c r="O73">
-        <v>-20.646221488</v>
+        <v>-21.10512601600001</v>
       </c>
       <c r="P73">
-        <v>-65.37970137866668</v>
+        <v>-66.8328990506667</v>
       </c>
       <c r="Q73">
-        <v>-43.77970137866669</v>
+        <v>-45.2328990506667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1496224395452523</v>
+        <v>0.1533303838147256</v>
       </c>
       <c r="T73">
-        <v>1.750595484293092</v>
+        <v>1.813116751589274</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08792034027069161</v>
+        <v>0.08669922443359865</v>
       </c>
       <c r="W73">
-        <v>0.2150683837641709</v>
+        <v>0.2153563228785574</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3663347511278817</v>
+        <v>0.3612467684733277</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1979890599406845</v>
+        <v>0.1998890599406845</v>
       </c>
       <c r="C74">
-        <v>-343.4651497213497</v>
+        <v>-353.4395476648513</v>
       </c>
       <c r="D74">
-        <v>151.2828502786503</v>
+        <v>149.4174523351488</v>
       </c>
       <c r="E74">
-        <v>269.0480000000001</v>
+        <v>277.1570000000001</v>
       </c>
       <c r="F74">
-        <v>583.8480000000001</v>
+        <v>591.9570000000001</v>
       </c>
       <c r="G74">
         <v>89.09999999999999</v>
@@ -7361,37 +7361,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M74">
-        <v>137.6713584</v>
+        <v>139.5834606</v>
       </c>
       <c r="N74">
-        <v>-87.9380250666667</v>
+        <v>-89.85012726666669</v>
       </c>
       <c r="O74">
-        <v>-21.10512601600001</v>
+        <v>-21.564030544</v>
       </c>
       <c r="P74">
-        <v>-66.8328990506667</v>
+        <v>-68.28609672266668</v>
       </c>
       <c r="Q74">
-        <v>-45.2328990506667</v>
+        <v>-46.68609672266669</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1533303838147256</v>
+        <v>0.1573129906226784</v>
       </c>
       <c r="T74">
-        <v>1.813116751589274</v>
+        <v>1.880269223870358</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08669922443359865</v>
+        <v>0.08551156382491923</v>
       </c>
       <c r="W74">
-        <v>0.2153563228785574</v>
+        <v>0.2156363732500841</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3612467684733277</v>
+        <v>0.3562981826038301</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1998890599406845</v>
+        <v>0.2017890599406845</v>
       </c>
       <c r="C75">
-        <v>-353.4395476648513</v>
+        <v>-363.3685032408688</v>
       </c>
       <c r="D75">
-        <v>149.4174523351488</v>
+        <v>147.5974967591312</v>
       </c>
       <c r="E75">
-        <v>277.1570000000001</v>
+        <v>285.266</v>
       </c>
       <c r="F75">
-        <v>591.9570000000001</v>
+        <v>600.066</v>
       </c>
       <c r="G75">
         <v>89.09999999999999</v>
@@ -7443,37 +7443,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M75">
-        <v>139.5834606</v>
+        <v>141.4955628</v>
       </c>
       <c r="N75">
-        <v>-89.85012726666669</v>
+        <v>-91.76222946666668</v>
       </c>
       <c r="O75">
-        <v>-21.564030544</v>
+        <v>-22.022935072</v>
       </c>
       <c r="P75">
-        <v>-68.28609672266668</v>
+        <v>-69.73929439466667</v>
       </c>
       <c r="Q75">
-        <v>-46.68609672266669</v>
+        <v>-48.13929439466668</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1573129906226784</v>
+        <v>0.1616019518004737</v>
       </c>
       <c r="T75">
-        <v>1.880269223870358</v>
+        <v>1.952587270942295</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08551156382491923</v>
+        <v>0.08435600215160952</v>
       </c>
       <c r="W75">
-        <v>0.2156363732500841</v>
+        <v>0.2159088546926505</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3562981826038301</v>
+        <v>0.351483342298373</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2017890599406845</v>
+        <v>0.2036890599406845</v>
       </c>
       <c r="C76">
-        <v>-363.3685032408688</v>
+        <v>-373.2536569778517</v>
       </c>
       <c r="D76">
-        <v>147.5974967591312</v>
+        <v>145.8213430221484</v>
       </c>
       <c r="E76">
-        <v>285.266</v>
+        <v>293.3750000000001</v>
       </c>
       <c r="F76">
-        <v>600.066</v>
+        <v>608.1750000000001</v>
       </c>
       <c r="G76">
         <v>89.09999999999999</v>
@@ -7525,37 +7525,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M76">
-        <v>141.4955628</v>
+        <v>143.407665</v>
       </c>
       <c r="N76">
-        <v>-91.76222946666668</v>
+        <v>-93.67433166666667</v>
       </c>
       <c r="O76">
-        <v>-22.022935072</v>
+        <v>-22.4818396</v>
       </c>
       <c r="P76">
-        <v>-69.73929439466667</v>
+        <v>-71.19249206666667</v>
       </c>
       <c r="Q76">
-        <v>-48.13929439466668</v>
+        <v>-49.59249206666668</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1616019518004737</v>
+        <v>0.1662340298724926</v>
       </c>
       <c r="T76">
-        <v>1.952587270942295</v>
+        <v>2.030690761779987</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08435600215160952</v>
+        <v>0.08323125545625473</v>
       </c>
       <c r="W76">
-        <v>0.2159088546926505</v>
+        <v>0.2161740699634151</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.351483342298373</v>
+        <v>0.3467968977343947</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2036890599406845</v>
+        <v>0.2055890599406845</v>
       </c>
       <c r="C77">
-        <v>-373.2536569778517</v>
+        <v>-383.0965713762774</v>
       </c>
       <c r="D77">
-        <v>145.8213430221484</v>
+        <v>144.0874286237227</v>
       </c>
       <c r="E77">
-        <v>293.3750000000001</v>
+        <v>301.4840000000001</v>
       </c>
       <c r="F77">
-        <v>608.1750000000001</v>
+        <v>616.2840000000001</v>
       </c>
       <c r="G77">
         <v>89.09999999999999</v>
@@ -7607,37 +7607,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M77">
-        <v>143.407665</v>
+        <v>145.3197672</v>
       </c>
       <c r="N77">
-        <v>-93.67433166666667</v>
+        <v>-95.5864338666667</v>
       </c>
       <c r="O77">
-        <v>-22.4818396</v>
+        <v>-22.94074412800001</v>
       </c>
       <c r="P77">
-        <v>-71.19249206666667</v>
+        <v>-72.64568973866669</v>
       </c>
       <c r="Q77">
-        <v>-49.59249206666668</v>
+        <v>-51.0456897386667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1662340298724926</v>
+        <v>0.1712521144505132</v>
       </c>
       <c r="T77">
-        <v>2.030690761779987</v>
+        <v>2.115302876854154</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08323125545625473</v>
+        <v>0.0821361073581461</v>
       </c>
       <c r="W77">
-        <v>0.2161740699634151</v>
+        <v>0.2164323058849492</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3467968977343947</v>
+        <v>0.3422337806589421</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2055890599406845</v>
+        <v>0.2074890599406845</v>
       </c>
       <c r="C78">
-        <v>-383.0965713762774</v>
+        <v>-392.8987354931664</v>
       </c>
       <c r="D78">
-        <v>144.0874286237227</v>
+        <v>142.3942645068337</v>
       </c>
       <c r="E78">
-        <v>301.4840000000001</v>
+        <v>309.593</v>
       </c>
       <c r="F78">
-        <v>616.2840000000001</v>
+        <v>624.393</v>
       </c>
       <c r="G78">
         <v>89.09999999999999</v>
@@ -7689,37 +7689,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M78">
-        <v>145.3197672</v>
+        <v>147.2318694</v>
       </c>
       <c r="N78">
-        <v>-95.5864338666667</v>
+        <v>-97.49853606666669</v>
       </c>
       <c r="O78">
-        <v>-22.94074412800001</v>
+        <v>-23.399648656</v>
       </c>
       <c r="P78">
-        <v>-72.64568973866669</v>
+        <v>-74.09888741066669</v>
       </c>
       <c r="Q78">
-        <v>-51.0456897386667</v>
+        <v>-52.4988874106667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1712521144505132</v>
+        <v>0.1767065542092311</v>
       </c>
       <c r="T78">
-        <v>2.115302876854154</v>
+        <v>2.20727256715216</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0821361073581461</v>
+        <v>0.08106940466518317</v>
       </c>
       <c r="W78">
-        <v>0.2164323058849492</v>
+        <v>0.2166838343799498</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3422337806589421</v>
+        <v>0.3377891861049298</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2074890599406845</v>
+        <v>0.2093890599406845</v>
       </c>
       <c r="C79">
-        <v>-392.8987354931664</v>
+        <v>-402.6615692071146</v>
       </c>
       <c r="D79">
-        <v>142.3942645068337</v>
+        <v>140.7404307928855</v>
       </c>
       <c r="E79">
-        <v>309.593</v>
+        <v>317.7020000000001</v>
       </c>
       <c r="F79">
-        <v>624.393</v>
+        <v>632.5020000000001</v>
       </c>
       <c r="G79">
         <v>89.09999999999999</v>
@@ -7771,37 +7771,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M79">
-        <v>147.2318694</v>
+        <v>149.1439716</v>
       </c>
       <c r="N79">
-        <v>-97.49853606666669</v>
+        <v>-99.41063826666668</v>
       </c>
       <c r="O79">
-        <v>-23.399648656</v>
+        <v>-23.858553184</v>
       </c>
       <c r="P79">
-        <v>-74.09888741066669</v>
+        <v>-75.55208508266668</v>
       </c>
       <c r="Q79">
-        <v>-52.4988874106667</v>
+        <v>-53.95208508266668</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1767065542092311</v>
+        <v>0.1826568521278326</v>
       </c>
       <c r="T79">
-        <v>2.20727256715216</v>
+        <v>2.307603138386349</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08106940466518317</v>
+        <v>0.08003005332332185</v>
       </c>
       <c r="W79">
-        <v>0.2166838343799498</v>
+        <v>0.2169289134263607</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3377891861049298</v>
+        <v>0.3334585555138411</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2093890599406845</v>
+        <v>0.2112890599406845</v>
       </c>
       <c r="C80">
-        <v>-402.6615692071146</v>
+        <v>-412.3864271895234</v>
       </c>
       <c r="D80">
-        <v>140.7404307928855</v>
+        <v>139.1245728104767</v>
       </c>
       <c r="E80">
-        <v>317.7020000000001</v>
+        <v>325.8110000000001</v>
       </c>
       <c r="F80">
-        <v>632.5020000000001</v>
+        <v>640.6110000000001</v>
       </c>
       <c r="G80">
         <v>89.09999999999999</v>
@@ -7853,37 +7853,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M80">
-        <v>149.1439716</v>
+        <v>151.0560738</v>
       </c>
       <c r="N80">
-        <v>-99.41063826666668</v>
+        <v>-101.3227404666667</v>
       </c>
       <c r="O80">
-        <v>-23.858553184</v>
+        <v>-24.31745771200001</v>
       </c>
       <c r="P80">
-        <v>-75.55208508266668</v>
+        <v>-77.00528275466669</v>
       </c>
       <c r="Q80">
-        <v>-53.95208508266668</v>
+        <v>-55.4052827546667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1826568521278326</v>
+        <v>0.1891738450863008</v>
       </c>
       <c r="T80">
-        <v>2.307603138386349</v>
+        <v>2.417489002119033</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08003005332332185</v>
+        <v>0.07901701467365953</v>
       </c>
       <c r="W80">
-        <v>0.2169289134263607</v>
+        <v>0.2171677879399511</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3334585555138411</v>
+        <v>0.329237561140248</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2112890599406845</v>
+        <v>0.2131890599406845</v>
       </c>
       <c r="C81">
-        <v>-412.3864271895234</v>
+        <v>-422.0746026053694</v>
       </c>
       <c r="D81">
-        <v>139.1245728104767</v>
+        <v>137.5453973946308</v>
       </c>
       <c r="E81">
-        <v>325.8110000000001</v>
+        <v>333.9200000000001</v>
       </c>
       <c r="F81">
-        <v>640.6110000000001</v>
+        <v>648.7200000000001</v>
       </c>
       <c r="G81">
         <v>89.09999999999999</v>
@@ -7935,37 +7935,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M81">
-        <v>151.0560738</v>
+        <v>152.968176</v>
       </c>
       <c r="N81">
-        <v>-101.3227404666667</v>
+        <v>-103.2348426666667</v>
       </c>
       <c r="O81">
-        <v>-24.31745771200001</v>
+        <v>-24.77636224</v>
       </c>
       <c r="P81">
-        <v>-77.00528275466669</v>
+        <v>-78.45848042666668</v>
       </c>
       <c r="Q81">
-        <v>-55.4052827546667</v>
+        <v>-56.85848042666669</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1891738450863008</v>
+        <v>0.1963425373406159</v>
       </c>
       <c r="T81">
-        <v>2.417489002119033</v>
+        <v>2.538363452224984</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07901701467365953</v>
+        <v>0.07802930199023879</v>
       </c>
       <c r="W81">
-        <v>0.2171677879399511</v>
+        <v>0.2174006905907017</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.329237561140248</v>
+        <v>0.3251220916259949</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2131890599406845</v>
+        <v>0.2150890599406846</v>
       </c>
       <c r="C82">
-        <v>-422.0746026053694</v>
+        <v>-431.7273305647625</v>
       </c>
       <c r="D82">
-        <v>137.5453973946308</v>
+        <v>136.0016694352376</v>
       </c>
       <c r="E82">
-        <v>333.9200000000001</v>
+        <v>342.0290000000001</v>
       </c>
       <c r="F82">
-        <v>648.7200000000001</v>
+        <v>656.8290000000001</v>
       </c>
       <c r="G82">
         <v>89.09999999999999</v>
@@ -8017,37 +8017,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M82">
-        <v>152.968176</v>
+        <v>154.8802782</v>
       </c>
       <c r="N82">
-        <v>-103.2348426666667</v>
+        <v>-105.1469448666667</v>
       </c>
       <c r="O82">
-        <v>-24.77636224</v>
+        <v>-25.235266768</v>
       </c>
       <c r="P82">
-        <v>-78.45848042666668</v>
+        <v>-79.91167809866668</v>
       </c>
       <c r="Q82">
-        <v>-56.85848042666669</v>
+        <v>-58.31167809866669</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1963425373406159</v>
+        <v>0.2042658287795957</v>
       </c>
       <c r="T82">
-        <v>2.538363452224984</v>
+        <v>2.671961528657879</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07802930199023879</v>
+        <v>0.07706597727430992</v>
       </c>
       <c r="W82">
-        <v>0.2174006905907017</v>
+        <v>0.2176278425587178</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3251220916259949</v>
+        <v>0.321108238642958</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2150890599406846</v>
+        <v>0.2169890599406845</v>
       </c>
       <c r="C83">
-        <v>-431.7273305647625</v>
+        <v>-441.3457913446538</v>
       </c>
       <c r="D83">
-        <v>136.0016694352376</v>
+        <v>134.4922086553463</v>
       </c>
       <c r="E83">
-        <v>342.0290000000001</v>
+        <v>350.1380000000001</v>
       </c>
       <c r="F83">
-        <v>656.8290000000001</v>
+        <v>664.9380000000001</v>
       </c>
       <c r="G83">
         <v>89.09999999999999</v>
@@ -8099,37 +8099,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M83">
-        <v>154.8802782</v>
+        <v>156.7923804</v>
       </c>
       <c r="N83">
-        <v>-105.1469448666667</v>
+        <v>-107.0590470666667</v>
       </c>
       <c r="O83">
-        <v>-25.235266768</v>
+        <v>-25.69417129600001</v>
       </c>
       <c r="P83">
-        <v>-79.91167809866668</v>
+        <v>-81.3648757706667</v>
       </c>
       <c r="Q83">
-        <v>-58.31167809866669</v>
+        <v>-59.76487577066671</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2042658287795957</v>
+        <v>0.2130694859340176</v>
       </c>
       <c r="T83">
-        <v>2.671961528657879</v>
+        <v>2.820403835805538</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07706597727430992</v>
+        <v>0.07612614828315978</v>
       </c>
       <c r="W83">
-        <v>0.2176278425587178</v>
+        <v>0.2178494542348309</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.321108238642958</v>
+        <v>0.3171922845131658</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2169890599406845</v>
+        <v>0.2188890599406845</v>
       </c>
       <c r="C84">
-        <v>-441.3457913446538</v>
+        <v>-450.931113398357</v>
       </c>
       <c r="D84">
-        <v>134.4922086553463</v>
+        <v>133.0158866016431</v>
       </c>
       <c r="E84">
-        <v>350.1380000000001</v>
+        <v>358.2470000000001</v>
       </c>
       <c r="F84">
-        <v>664.9380000000001</v>
+        <v>673.0470000000001</v>
       </c>
       <c r="G84">
         <v>89.09999999999999</v>
@@ -8181,37 +8181,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M84">
-        <v>156.7923804</v>
+        <v>158.7044826</v>
       </c>
       <c r="N84">
-        <v>-107.0590470666667</v>
+        <v>-108.9711492666667</v>
       </c>
       <c r="O84">
-        <v>-25.69417129600001</v>
+        <v>-26.15307582400001</v>
       </c>
       <c r="P84">
-        <v>-81.3648757706667</v>
+        <v>-82.8180734426667</v>
       </c>
       <c r="Q84">
-        <v>-59.76487577066671</v>
+        <v>-61.21807344266671</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2130694859340176</v>
+        <v>0.2229088674595481</v>
       </c>
       <c r="T84">
-        <v>2.820403835805538</v>
+        <v>2.9863099437941</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07612614828315978</v>
+        <v>0.07520896577372413</v>
       </c>
       <c r="W84">
-        <v>0.2178494542348309</v>
+        <v>0.2180657258705559</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3171922845131658</v>
+        <v>0.3133706907238506</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2188890599406845</v>
+        <v>0.2207890599406845</v>
       </c>
       <c r="C85">
-        <v>-450.931113398357</v>
+        <v>-460.4843761690056</v>
       </c>
       <c r="D85">
-        <v>133.0158866016431</v>
+        <v>131.5716238309946</v>
       </c>
       <c r="E85">
-        <v>358.2470000000001</v>
+        <v>366.3560000000002</v>
       </c>
       <c r="F85">
-        <v>673.0470000000001</v>
+        <v>681.1560000000002</v>
       </c>
       <c r="G85">
         <v>89.09999999999999</v>
@@ -8263,37 +8263,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M85">
-        <v>158.7044826</v>
+        <v>160.6165848000001</v>
       </c>
       <c r="N85">
-        <v>-108.9711492666667</v>
+        <v>-110.8832514666667</v>
       </c>
       <c r="O85">
-        <v>-26.15307582400001</v>
+        <v>-26.61198035200001</v>
       </c>
       <c r="P85">
-        <v>-82.8180734426667</v>
+        <v>-84.27127111466672</v>
       </c>
       <c r="Q85">
-        <v>-61.21807344266671</v>
+        <v>-62.67127111466672</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2229088674595481</v>
+        <v>0.2339781716757698</v>
       </c>
       <c r="T85">
-        <v>2.9863099437941</v>
+        <v>3.172954315281231</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07520896577372413</v>
+        <v>0.07431362094308455</v>
       </c>
       <c r="W85">
-        <v>0.2180657258705559</v>
+        <v>0.2182768481816207</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3133706907238506</v>
+        <v>0.3096400872628523</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2207890599406845</v>
+        <v>0.2226890599406845</v>
       </c>
       <c r="C86">
-        <v>-460.4843761690053</v>
+        <v>-470.006612721694</v>
       </c>
       <c r="D86">
-        <v>131.5716238309948</v>
+        <v>130.1583872783062</v>
       </c>
       <c r="E86">
-        <v>366.3560000000001</v>
+        <v>374.4650000000001</v>
       </c>
       <c r="F86">
-        <v>681.1560000000001</v>
+        <v>689.2650000000001</v>
       </c>
       <c r="G86">
         <v>89.09999999999999</v>
@@ -8345,37 +8345,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M86">
-        <v>160.6165848</v>
+        <v>162.528687</v>
       </c>
       <c r="N86">
-        <v>-110.8832514666667</v>
+        <v>-112.7953536666667</v>
       </c>
       <c r="O86">
-        <v>-26.61198035200001</v>
+        <v>-27.07088488</v>
       </c>
       <c r="P86">
-        <v>-84.27127111466669</v>
+        <v>-85.72446878666668</v>
       </c>
       <c r="Q86">
-        <v>-62.67127111466669</v>
+        <v>-64.12446878666668</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2339781716757698</v>
+        <v>0.2465233831208211</v>
       </c>
       <c r="T86">
-        <v>3.172954315281229</v>
+        <v>3.384484602966645</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07431362094308457</v>
+        <v>0.07343934304963651</v>
       </c>
       <c r="W86">
-        <v>0.2182768481816207</v>
+        <v>0.2184830029088957</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3096400872628524</v>
+        <v>0.3059972627068188</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2226890599406845</v>
+        <v>0.2245890599406845</v>
       </c>
       <c r="C87">
-        <v>-470.006612721694</v>
+        <v>-479.4988122077857</v>
       </c>
       <c r="D87">
-        <v>130.1583872783062</v>
+        <v>128.7751877922143</v>
       </c>
       <c r="E87">
-        <v>374.4650000000001</v>
+        <v>382.574</v>
       </c>
       <c r="F87">
-        <v>689.2650000000001</v>
+        <v>697.374</v>
       </c>
       <c r="G87">
         <v>89.09999999999999</v>
@@ -8427,37 +8427,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M87">
-        <v>162.528687</v>
+        <v>164.4407892</v>
       </c>
       <c r="N87">
-        <v>-112.7953536666667</v>
+        <v>-114.7074558666667</v>
       </c>
       <c r="O87">
-        <v>-27.07088488</v>
+        <v>-27.529789408</v>
       </c>
       <c r="P87">
-        <v>-85.72446878666668</v>
+        <v>-87.17766645866668</v>
       </c>
       <c r="Q87">
-        <v>-64.12446878666668</v>
+        <v>-65.57766645866668</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2465233831208211</v>
+        <v>0.2608607676294512</v>
       </c>
       <c r="T87">
-        <v>3.384484602966645</v>
+        <v>3.626233503178548</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07343934304963651</v>
+        <v>0.07258539720022214</v>
       </c>
       <c r="W87">
-        <v>0.2184830029088957</v>
+        <v>0.2186843633401876</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3059972627068188</v>
+        <v>0.3024391550009256</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2245890599406845</v>
+        <v>0.2264890599406846</v>
       </c>
       <c r="C88">
-        <v>-479.4988122077857</v>
+        <v>-488.9619221737433</v>
       </c>
       <c r="D88">
-        <v>128.7751877922143</v>
+        <v>127.4210778262567</v>
       </c>
       <c r="E88">
-        <v>382.574</v>
+        <v>390.683</v>
       </c>
       <c r="F88">
-        <v>697.374</v>
+        <v>705.4830000000001</v>
       </c>
       <c r="G88">
         <v>89.09999999999999</v>
@@ -8509,37 +8509,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M88">
-        <v>164.4407892</v>
+        <v>166.3528914</v>
       </c>
       <c r="N88">
-        <v>-114.7074558666667</v>
+        <v>-116.6195580666667</v>
       </c>
       <c r="O88">
-        <v>-27.529789408</v>
+        <v>-27.98869393600001</v>
       </c>
       <c r="P88">
-        <v>-87.17766645866668</v>
+        <v>-88.63086413066669</v>
       </c>
       <c r="Q88">
-        <v>-65.57766645866668</v>
+        <v>-67.0308641306667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2608607676294512</v>
+        <v>0.2774039036009474</v>
       </c>
       <c r="T88">
-        <v>3.626233503178548</v>
+        <v>3.905174541884591</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07258539720022214</v>
+        <v>0.07175108228987474</v>
       </c>
       <c r="W88">
-        <v>0.2186843633401876</v>
+        <v>0.2188810947960476</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3024391550009256</v>
+        <v>0.2989628428744782</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2264890599406846</v>
+        <v>0.2283890599406845</v>
       </c>
       <c r="C89">
-        <v>-488.9619221737433</v>
+        <v>-498.3968507258076</v>
       </c>
       <c r="D89">
-        <v>127.4210778262567</v>
+        <v>126.0951492741926</v>
       </c>
       <c r="E89">
-        <v>390.683</v>
+        <v>398.7920000000001</v>
       </c>
       <c r="F89">
-        <v>705.4830000000001</v>
+        <v>713.5920000000001</v>
       </c>
       <c r="G89">
         <v>89.09999999999999</v>
@@ -8591,37 +8591,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M89">
-        <v>166.3528914</v>
+        <v>168.2649936</v>
       </c>
       <c r="N89">
-        <v>-116.6195580666667</v>
+        <v>-118.5316602666667</v>
       </c>
       <c r="O89">
-        <v>-27.98869393600001</v>
+        <v>-28.44759846400001</v>
       </c>
       <c r="P89">
-        <v>-88.63086413066669</v>
+        <v>-90.08406180266668</v>
       </c>
       <c r="Q89">
-        <v>-67.0308641306667</v>
+        <v>-68.48406180266669</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2774039036009474</v>
+        <v>0.2967042289010264</v>
       </c>
       <c r="T89">
-        <v>3.905174541884591</v>
+        <v>4.230605753708307</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07175108228987474</v>
+        <v>0.07093572908203526</v>
       </c>
       <c r="W89">
-        <v>0.2188810947960476</v>
+        <v>0.2190733550824561</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2989628428744782</v>
+        <v>0.2955655378418136</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2283890599406845</v>
+        <v>0.2302890599406845</v>
       </c>
       <c r="C90">
-        <v>-498.3968507258076</v>
+        <v>-507.8044685609138</v>
       </c>
       <c r="D90">
-        <v>126.0951492741926</v>
+        <v>124.7965314390863</v>
       </c>
       <c r="E90">
-        <v>398.7920000000001</v>
+        <v>406.9010000000001</v>
       </c>
       <c r="F90">
-        <v>713.5920000000001</v>
+        <v>721.7010000000001</v>
       </c>
       <c r="G90">
         <v>89.09999999999999</v>
@@ -8673,37 +8673,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M90">
-        <v>168.2649936</v>
+        <v>170.1770958</v>
       </c>
       <c r="N90">
-        <v>-118.5316602666667</v>
+        <v>-120.4437624666667</v>
       </c>
       <c r="O90">
-        <v>-28.44759846400001</v>
+        <v>-28.90650299200001</v>
       </c>
       <c r="P90">
-        <v>-90.08406180266668</v>
+        <v>-91.5372594746667</v>
       </c>
       <c r="Q90">
-        <v>-68.48406180266669</v>
+        <v>-69.9372594746667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2967042289010264</v>
+        <v>0.3195137042556651</v>
       </c>
       <c r="T90">
-        <v>4.230605753708307</v>
+        <v>4.615206276772698</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07093572908203526</v>
+        <v>0.07013869841819216</v>
       </c>
       <c r="W90">
-        <v>0.2190733550824561</v>
+        <v>0.2192612949129903</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2955655378418136</v>
+        <v>0.2922445767424674</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2302890599406845</v>
+        <v>0.2321890599406845</v>
       </c>
       <c r="C91">
-        <v>-507.8044685609138</v>
+        <v>-517.1856108733957</v>
       </c>
       <c r="D91">
-        <v>124.7965314390863</v>
+        <v>123.5243891266044</v>
       </c>
       <c r="E91">
-        <v>406.9010000000001</v>
+        <v>415.01</v>
       </c>
       <c r="F91">
-        <v>721.7010000000001</v>
+        <v>729.8100000000001</v>
       </c>
       <c r="G91">
         <v>89.09999999999999</v>
@@ -8755,37 +8755,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M91">
-        <v>170.1770958</v>
+        <v>172.089198</v>
       </c>
       <c r="N91">
-        <v>-120.4437624666667</v>
+        <v>-122.3558646666667</v>
       </c>
       <c r="O91">
-        <v>-28.90650299200001</v>
+        <v>-29.36540752</v>
       </c>
       <c r="P91">
-        <v>-91.5372594746667</v>
+        <v>-92.99045714666667</v>
       </c>
       <c r="Q91">
-        <v>-69.9372594746667</v>
+        <v>-71.39045714666668</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3195137042556651</v>
+        <v>0.3468850746812316</v>
       </c>
       <c r="T91">
-        <v>4.615206276772698</v>
+        <v>5.076726904449968</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07013869841819216</v>
+        <v>0.06935937954687894</v>
       </c>
       <c r="W91">
-        <v>0.2192612949129903</v>
+        <v>0.2194450583028459</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2922445767424674</v>
+        <v>0.2889974147786623</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2321890599406845</v>
+        <v>0.2340890599406845</v>
       </c>
       <c r="C92">
-        <v>-517.1856108733957</v>
+        <v>-526.5410791462443</v>
       </c>
       <c r="D92">
-        <v>123.5243891266044</v>
+        <v>122.2779208537558</v>
       </c>
       <c r="E92">
-        <v>415.01</v>
+        <v>423.1190000000001</v>
       </c>
       <c r="F92">
-        <v>729.8100000000001</v>
+        <v>737.9190000000001</v>
       </c>
       <c r="G92">
         <v>89.09999999999999</v>
@@ -8837,37 +8837,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M92">
-        <v>172.089198</v>
+        <v>174.0013002</v>
       </c>
       <c r="N92">
-        <v>-122.3558646666667</v>
+        <v>-124.2679668666667</v>
       </c>
       <c r="O92">
-        <v>-29.36540752</v>
+        <v>-29.82431204800001</v>
       </c>
       <c r="P92">
-        <v>-92.99045714666667</v>
+        <v>-94.44365481866669</v>
       </c>
       <c r="Q92">
-        <v>-71.39045714666668</v>
+        <v>-72.84365481866669</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3468850746812316</v>
+        <v>0.3803389718680352</v>
       </c>
       <c r="T92">
-        <v>5.076726904449968</v>
+        <v>5.640807671611077</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06935937954687894</v>
+        <v>0.06859718856284729</v>
       </c>
       <c r="W92">
-        <v>0.2194450583028459</v>
+        <v>0.2196247829368806</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2889974147786623</v>
+        <v>0.2858216190118638</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2340890599406845</v>
+        <v>0.2359890599406845</v>
       </c>
       <c r="C93">
-        <v>-526.5410791462443</v>
+        <v>-535.8716428350001</v>
       </c>
       <c r="D93">
-        <v>122.2779208537558</v>
+        <v>121.056357165</v>
       </c>
       <c r="E93">
-        <v>423.1190000000001</v>
+        <v>431.2280000000001</v>
       </c>
       <c r="F93">
-        <v>737.9190000000001</v>
+        <v>746.0280000000001</v>
       </c>
       <c r="G93">
         <v>89.09999999999999</v>
@@ -8919,37 +8919,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M93">
-        <v>174.0013002</v>
+        <v>175.9134024000001</v>
       </c>
       <c r="N93">
-        <v>-124.2679668666667</v>
+        <v>-126.1800690666667</v>
       </c>
       <c r="O93">
-        <v>-29.82431204800001</v>
+        <v>-30.28321657600001</v>
       </c>
       <c r="P93">
-        <v>-94.44365481866669</v>
+        <v>-95.8968524906667</v>
       </c>
       <c r="Q93">
-        <v>-72.84365481866669</v>
+        <v>-74.29685249066671</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3803389718680352</v>
+        <v>0.4221563433515397</v>
       </c>
       <c r="T93">
-        <v>5.640807671611077</v>
+        <v>6.345908630562463</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06859718856284729</v>
+        <v>0.06785156694803372</v>
       </c>
       <c r="W93">
-        <v>0.2196247829368806</v>
+        <v>0.2198006005136537</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2858216190118638</v>
+        <v>0.2827148622834739</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2359890599406845</v>
+        <v>0.2378890599406845</v>
       </c>
       <c r="C94">
-        <v>-535.8716428350001</v>
+        <v>-545.1780409517098</v>
       </c>
       <c r="D94">
-        <v>121.056357165</v>
+        <v>119.8589590482904</v>
       </c>
       <c r="E94">
-        <v>431.2280000000001</v>
+        <v>439.3370000000002</v>
       </c>
       <c r="F94">
-        <v>746.0280000000001</v>
+        <v>754.1370000000002</v>
       </c>
       <c r="G94">
         <v>89.09999999999999</v>
@@ -9001,37 +9001,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M94">
-        <v>175.9134024000001</v>
+        <v>177.8255046</v>
       </c>
       <c r="N94">
-        <v>-126.1800690666667</v>
+        <v>-128.0921712666667</v>
       </c>
       <c r="O94">
-        <v>-30.28321657600001</v>
+        <v>-30.74212110400001</v>
       </c>
       <c r="P94">
-        <v>-95.8968524906667</v>
+        <v>-97.35005016266669</v>
       </c>
       <c r="Q94">
-        <v>-74.29685249066671</v>
+        <v>-75.7500501626667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4221563433515397</v>
+        <v>0.4759215352589026</v>
       </c>
       <c r="T94">
-        <v>6.345908630562463</v>
+        <v>7.252467006357102</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06785156694803372</v>
+        <v>0.06712198020665702</v>
       </c>
       <c r="W94">
-        <v>0.2198006005136537</v>
+        <v>0.2199726370672703</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2827148622834739</v>
+        <v>0.2796749175277377</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2378890599406845</v>
+        <v>0.2397890599406845</v>
       </c>
       <c r="C95">
-        <v>-545.1780409517098</v>
+        <v>-554.4609835557997</v>
       </c>
       <c r="D95">
-        <v>119.8589590482904</v>
+        <v>118.6850164442005</v>
       </c>
       <c r="E95">
-        <v>439.3370000000002</v>
+        <v>447.4460000000001</v>
       </c>
       <c r="F95">
-        <v>754.1370000000002</v>
+        <v>762.2460000000001</v>
       </c>
       <c r="G95">
         <v>89.09999999999999</v>
@@ -9083,37 +9083,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M95">
-        <v>177.8255046</v>
+        <v>179.7376068</v>
       </c>
       <c r="N95">
-        <v>-128.0921712666667</v>
+        <v>-130.0042734666667</v>
       </c>
       <c r="O95">
-        <v>-30.74212110400001</v>
+        <v>-31.201025632</v>
       </c>
       <c r="P95">
-        <v>-97.35005016266669</v>
+        <v>-98.80324783466668</v>
       </c>
       <c r="Q95">
-        <v>-75.7500501626667</v>
+        <v>-77.20324783466668</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4759215352589026</v>
+        <v>0.547608457802053</v>
       </c>
       <c r="T95">
-        <v>7.252467006357102</v>
+        <v>8.461211507416619</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06712198020665702</v>
+        <v>0.06640791658743726</v>
       </c>
       <c r="W95">
-        <v>0.2199726370672703</v>
+        <v>0.2201410132686823</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2796749175277377</v>
+        <v>0.2766996524476554</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2397890599406845</v>
+        <v>0.2416890599406845</v>
       </c>
       <c r="C96">
-        <v>-554.4609835557997</v>
+        <v>-563.7211531581873</v>
       </c>
       <c r="D96">
-        <v>118.6850164442005</v>
+        <v>117.5338468418128</v>
       </c>
       <c r="E96">
-        <v>447.4460000000001</v>
+        <v>455.5550000000001</v>
       </c>
       <c r="F96">
-        <v>762.2460000000001</v>
+        <v>770.3550000000001</v>
       </c>
       <c r="G96">
         <v>89.09999999999999</v>
@@ -9165,37 +9165,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M96">
-        <v>179.7376068</v>
+        <v>181.649709</v>
       </c>
       <c r="N96">
-        <v>-130.0042734666667</v>
+        <v>-131.9163756666667</v>
       </c>
       <c r="O96">
-        <v>-31.201025632</v>
+        <v>-31.65993016</v>
       </c>
       <c r="P96">
-        <v>-98.80324783466668</v>
+        <v>-100.2564455066667</v>
       </c>
       <c r="Q96">
-        <v>-77.20324783466668</v>
+        <v>-78.65644550666669</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.547608457802053</v>
+        <v>0.647970149362464</v>
       </c>
       <c r="T96">
-        <v>8.461211507416619</v>
+        <v>10.15345380889995</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06640791658743726</v>
+        <v>0.06570888588651687</v>
       </c>
       <c r="W96">
-        <v>0.2201410132686823</v>
+        <v>0.2203058447079593</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2766996524476554</v>
+        <v>0.2737870245271538</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2416890599406845</v>
+        <v>0.2435890599406845</v>
       </c>
       <c r="C97">
-        <v>-563.7211531581873</v>
+        <v>-572.9592060444613</v>
       </c>
       <c r="D97">
-        <v>117.5338468418128</v>
+        <v>116.4047939555389</v>
       </c>
       <c r="E97">
-        <v>455.5550000000001</v>
+        <v>463.6640000000002</v>
       </c>
       <c r="F97">
-        <v>770.3550000000001</v>
+        <v>778.4640000000002</v>
       </c>
       <c r="G97">
         <v>89.09999999999999</v>
@@ -9247,37 +9247,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M97">
-        <v>181.649709</v>
+        <v>183.5618112000001</v>
       </c>
       <c r="N97">
-        <v>-131.9163756666667</v>
+        <v>-133.8284778666667</v>
       </c>
       <c r="O97">
-        <v>-31.65993016</v>
+        <v>-32.11883468800001</v>
       </c>
       <c r="P97">
-        <v>-100.2564455066667</v>
+        <v>-101.7096431786667</v>
       </c>
       <c r="Q97">
-        <v>-78.65644550666669</v>
+        <v>-80.10964317866672</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.647970149362464</v>
+        <v>0.7985126867030804</v>
       </c>
       <c r="T97">
-        <v>10.15345380889995</v>
+        <v>12.69181726112494</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06570888588651687</v>
+        <v>0.06502441832519899</v>
       </c>
       <c r="W97">
-        <v>0.2203058447079593</v>
+        <v>0.2204672421589181</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2737870245271538</v>
+        <v>0.2709350763549957</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2435890599406845</v>
+        <v>0.2454890599406845</v>
       </c>
       <c r="C98">
-        <v>-572.9592060444611</v>
+        <v>-582.1757735225256</v>
       </c>
       <c r="D98">
-        <v>116.404793955539</v>
+        <v>115.2972264774746</v>
       </c>
       <c r="E98">
-        <v>463.664</v>
+        <v>471.7730000000001</v>
       </c>
       <c r="F98">
-        <v>778.4640000000001</v>
+        <v>786.5730000000001</v>
       </c>
       <c r="G98">
         <v>89.09999999999999</v>
@@ -9329,37 +9329,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M98">
-        <v>183.5618112</v>
+        <v>185.4739134</v>
       </c>
       <c r="N98">
-        <v>-133.8284778666667</v>
+        <v>-135.7405800666667</v>
       </c>
       <c r="O98">
-        <v>-32.118834688</v>
+        <v>-32.57773921600001</v>
       </c>
       <c r="P98">
-        <v>-101.7096431786667</v>
+        <v>-103.1628408506667</v>
       </c>
       <c r="Q98">
-        <v>-80.10964317866669</v>
+        <v>-81.56284085066672</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7985126867030784</v>
+        <v>1.049416915604105</v>
       </c>
       <c r="T98">
-        <v>12.69181726112491</v>
+        <v>16.92242301483321</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06502441832519899</v>
+        <v>0.06435406349710415</v>
       </c>
       <c r="W98">
-        <v>0.2204672421589181</v>
+        <v>0.2206253118273828</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2709350763549959</v>
+        <v>0.268141931237934</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2454890599406845</v>
+        <v>0.2473890599406845</v>
       </c>
       <c r="C99">
-        <v>-582.1757735225256</v>
+        <v>-591.3714630996863</v>
       </c>
       <c r="D99">
-        <v>115.2972264774746</v>
+        <v>114.2105369003138</v>
       </c>
       <c r="E99">
-        <v>471.7730000000001</v>
+        <v>479.8820000000001</v>
       </c>
       <c r="F99">
-        <v>786.5730000000001</v>
+        <v>794.6820000000001</v>
       </c>
       <c r="G99">
         <v>89.09999999999999</v>
@@ -9411,37 +9411,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M99">
-        <v>185.4739134</v>
+        <v>187.3860156</v>
       </c>
       <c r="N99">
-        <v>-135.7405800666667</v>
+        <v>-137.6526822666667</v>
       </c>
       <c r="O99">
-        <v>-32.57773921600001</v>
+        <v>-33.03664374400001</v>
       </c>
       <c r="P99">
-        <v>-103.1628408506667</v>
+        <v>-104.6160385226667</v>
       </c>
       <c r="Q99">
-        <v>-81.56284085066672</v>
+        <v>-83.01603852266672</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.049416915604105</v>
+        <v>1.551225373406157</v>
       </c>
       <c r="T99">
-        <v>16.92242301483321</v>
+        <v>25.38363452224982</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06435406349710415</v>
+        <v>0.06369738937978676</v>
       </c>
       <c r="W99">
-        <v>0.2206253118273828</v>
+        <v>0.2207801555842463</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.268141931237934</v>
+        <v>0.2654057890824448</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2473890599406845</v>
+        <v>0.2492890599406845</v>
       </c>
       <c r="C100">
-        <v>-591.3714630996863</v>
+        <v>-600.5468595937969</v>
       </c>
       <c r="D100">
-        <v>114.2105369003138</v>
+        <v>113.1441404062033</v>
       </c>
       <c r="E100">
-        <v>479.8820000000001</v>
+        <v>487.991</v>
       </c>
       <c r="F100">
-        <v>794.6820000000001</v>
+        <v>802.7910000000001</v>
       </c>
       <c r="G100">
         <v>89.09999999999999</v>
@@ -9493,37 +9493,37 @@
         <v>49.73333333333333</v>
       </c>
       <c r="M100">
-        <v>187.3860156</v>
+        <v>189.2981178</v>
       </c>
       <c r="N100">
-        <v>-137.6526822666667</v>
+        <v>-139.5647844666667</v>
       </c>
       <c r="O100">
-        <v>-33.03664374400001</v>
+        <v>-33.49554827200001</v>
       </c>
       <c r="P100">
-        <v>-104.6160385226667</v>
+        <v>-106.0692361946667</v>
       </c>
       <c r="Q100">
-        <v>-83.01603852266672</v>
+        <v>-84.46923619466671</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.551225373406157</v>
+        <v>3.056650746812314</v>
       </c>
       <c r="T100">
-        <v>25.38363452224982</v>
+        <v>50.76726904449963</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06369738937978676</v>
+        <v>0.06305398140625357</v>
       </c>
       <c r="W100">
-        <v>0.2207801555842463</v>
+        <v>0.2209318711844054</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2654057890824448</v>
+        <v>0.2627249225260565</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2492890599406845</v>
-      </c>
-      <c r="C101">
-        <v>-600.5468595937969</v>
-      </c>
-      <c r="D101">
-        <v>113.1441404062033</v>
-      </c>
-      <c r="E101">
-        <v>487.991</v>
-      </c>
-      <c r="F101">
-        <v>802.7910000000001</v>
-      </c>
-      <c r="G101">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>496.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>71.33333333333333</v>
-      </c>
-      <c r="K101">
-        <v>21.6</v>
-      </c>
-      <c r="L101">
-        <v>49.73333333333333</v>
-      </c>
-      <c r="M101">
-        <v>189.2981178</v>
-      </c>
-      <c r="N101">
-        <v>-139.5647844666667</v>
-      </c>
-      <c r="O101">
-        <v>-33.49554827200001</v>
-      </c>
-      <c r="P101">
-        <v>-106.0692361946667</v>
-      </c>
-      <c r="Q101">
-        <v>-84.46923619466671</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.056650746812314</v>
-      </c>
-      <c r="T101">
-        <v>50.76726904449963</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06305398140625357</v>
-      </c>
-      <c r="W101">
-        <v>0.2209318711844054</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2627249225260565</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
